--- a/results/01_pollution_assessment/SumRel_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4732683672767806</v>
+        <v>0.5165489478689989</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05346326544643887</v>
+        <v>0.03309789573799771</v>
       </c>
       <c r="F2" t="n">
-        <v>0.898499991029527</v>
+        <v>1.068461730700772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.582</v>
+        <v>0.435</v>
       </c>
       <c r="H2" t="n">
-        <v>156.7954575667775</v>
+        <v>2.444897096111021</v>
       </c>
       <c r="I2" t="n">
-        <v>331.3034810861955</v>
+        <v>4.733137307117441</v>
       </c>
       <c r="J2" t="n">
-        <v>7.56034671514944</v>
+        <v>0.1387412910586835</v>
       </c>
       <c r="K2" t="n">
-        <v>12.05578588905673</v>
+        <v>9.145636738102082</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3562752562317958</v>
+        <v>0.4259668859313568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03441288434769363</v>
+        <v>0.1389503288970352</v>
       </c>
       <c r="F3" t="n">
-        <v>1.106918010161452</v>
+        <v>1.484119558581491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.374</v>
+        <v>0.121</v>
       </c>
       <c r="H3" t="n">
-        <v>172.2227885178943</v>
+        <v>3.186719447168445</v>
       </c>
       <c r="I3" t="n">
-        <v>483.3981184644624</v>
+        <v>7.481143610965981</v>
       </c>
       <c r="J3" t="n">
-        <v>5.09982718025669</v>
+        <v>0.1075146359929333</v>
       </c>
       <c r="K3" t="n">
-        <v>9.45177088954156</v>
+        <v>7.066033920197936</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3291177434076929</v>
+        <v>0.36741205445111</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08951693748186884</v>
+        <v>0.1414877881836492</v>
       </c>
       <c r="F4" t="n">
-        <v>1.373608666030873</v>
+        <v>1.626262023647114</v>
       </c>
       <c r="G4" t="n">
-        <v>0.141</v>
+        <v>0.067</v>
       </c>
       <c r="H4" t="n">
-        <v>203.4055946221505</v>
+        <v>3.589090543528475</v>
       </c>
       <c r="I4" t="n">
-        <v>618.0329037142883</v>
+        <v>9.768570464815983</v>
       </c>
       <c r="J4" t="n">
-        <v>4.280567222953431</v>
+        <v>0.127760008516781</v>
       </c>
       <c r="K4" t="n">
-        <v>9.20027890551199</v>
+        <v>5.906324511842218</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2257702959554279</v>
+        <v>0.2974187109294179</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02202563699632998</v>
+        <v>0.1125288980161068</v>
       </c>
       <c r="F5" t="n">
-        <v>1.108104119680269</v>
+        <v>1.608626815306845</v>
       </c>
       <c r="G5" t="n">
-        <v>0.346</v>
+        <v>0.083</v>
       </c>
       <c r="H5" t="n">
-        <v>163.447971514266</v>
+        <v>3.81811964404275</v>
       </c>
       <c r="I5" t="n">
-        <v>723.9569351786397</v>
+        <v>12.83752334246667</v>
       </c>
       <c r="J5" t="n">
-        <v>3.204908461053476</v>
+        <v>0.1129046677733935</v>
       </c>
       <c r="K5" t="n">
-        <v>8.894886136743045</v>
+        <v>6.062995790074879</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2180456892099787</v>
+        <v>0.249875983412775</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05513854112872429</v>
+        <v>0.09360014662376992</v>
       </c>
       <c r="F6" t="n">
-        <v>1.338466063510132</v>
+        <v>1.598941900084934</v>
       </c>
       <c r="G6" t="n">
-        <v>0.16</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>199.3740236023656</v>
+        <v>3.813291732885132</v>
       </c>
       <c r="I6" t="n">
-        <v>914.3681047982918</v>
+        <v>15.26073726975946</v>
       </c>
       <c r="J6" t="n">
-        <v>2.897002694468576</v>
+        <v>0.09806913748105053</v>
       </c>
       <c r="K6" t="n">
-        <v>7.145205485892123</v>
+        <v>3.372238329751428</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1924360153921696</v>
+        <v>0.1693782491600118</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04822816099791416</v>
+        <v>0.02105293651001383</v>
       </c>
       <c r="F7" t="n">
-        <v>1.334435050022042</v>
+        <v>1.141937583908502</v>
       </c>
       <c r="G7" t="n">
-        <v>0.143</v>
+        <v>0.31</v>
       </c>
       <c r="H7" t="n">
-        <v>198.2957055806359</v>
+        <v>2.888125564650369</v>
       </c>
       <c r="I7" t="n">
-        <v>1030.450070255948</v>
+        <v>17.05133675057625</v>
       </c>
       <c r="J7" t="n">
-        <v>2.825316517609244</v>
+        <v>0.05254961479562898</v>
       </c>
       <c r="K7" t="n">
-        <v>7.553020469081215</v>
+        <v>3.75034946795072</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1630798948119615</v>
+        <v>0.168227876094482</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03627381826831921</v>
+        <v>0.04220179671485791</v>
       </c>
       <c r="F8" t="n">
-        <v>1.286057413469733</v>
+        <v>1.334865584350482</v>
       </c>
       <c r="G8" t="n">
-        <v>0.177</v>
+        <v>0.167</v>
       </c>
       <c r="H8" t="n">
-        <v>189.5831286459287</v>
+        <v>3.205177317793258</v>
       </c>
       <c r="I8" t="n">
-        <v>1162.51686858473</v>
+        <v>19.05259337633872</v>
       </c>
       <c r="J8" t="n">
-        <v>2.48093535933162</v>
+        <v>0.05829159907333734</v>
       </c>
       <c r="K8" t="n">
-        <v>4.769052228048605</v>
+        <v>3.535358492741626</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1874705367594466</v>
+        <v>0.1517964992571969</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0805587652804266</v>
+        <v>0.04019077547524919</v>
       </c>
       <c r="F9" t="n">
-        <v>1.753506972768054</v>
+        <v>1.360113927075754</v>
       </c>
       <c r="G9" t="n">
-        <v>0.018</v>
+        <v>0.155</v>
       </c>
       <c r="H9" t="n">
-        <v>245.5434752998656</v>
+        <v>3.167325878216349</v>
       </c>
       <c r="I9" t="n">
-        <v>1309.77101545794</v>
+        <v>20.86560555556542</v>
       </c>
       <c r="J9" t="n">
-        <v>2.711639476193534</v>
+        <v>0.05028892640603198</v>
       </c>
       <c r="K9" t="n">
-        <v>4.03805351020528</v>
+        <v>3.860154330167111</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1985352754801058</v>
+        <v>0.1752176576077353</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1031228082753566</v>
+        <v>0.07702928351341809</v>
       </c>
       <c r="F10" t="n">
-        <v>2.080810624612204</v>
+        <v>1.784505133361571</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008</v>
+        <v>0.038</v>
       </c>
       <c r="H10" t="n">
-        <v>292.719911962232</v>
+        <v>3.905079307182867</v>
       </c>
       <c r="I10" t="n">
-        <v>1474.397490593876</v>
+        <v>22.28701924508817</v>
       </c>
       <c r="J10" t="n">
-        <v>3.763810492982985</v>
+        <v>0.05877437848956074</v>
       </c>
       <c r="K10" t="n">
-        <v>2.816104384311583</v>
+        <v>3.485812317750533</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1963399048852085</v>
+        <v>0.1903949125714409</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1108441500857625</v>
+        <v>0.1042667117811686</v>
       </c>
       <c r="F11" t="n">
-        <v>2.296487180512979</v>
+        <v>2.210598977158073</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="H11" t="n">
-        <v>307.6467497106757</v>
+        <v>4.775101986962683</v>
       </c>
       <c r="I11" t="n">
-        <v>1566.908927100395</v>
+        <v>25.07998728784807</v>
       </c>
       <c r="J11" t="n">
-        <v>3.619071503598446</v>
+        <v>0.0726045339019856</v>
       </c>
       <c r="K11" t="n">
-        <v>2.558475407505203</v>
+        <v>3.026876285456252</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2165771273657132</v>
+        <v>0.1806201326712163</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1412480049970316</v>
+        <v>0.1018336069665255</v>
       </c>
       <c r="F12" t="n">
-        <v>2.875078330339828</v>
+        <v>2.292525670547022</v>
       </c>
       <c r="G12" t="n">
         <v>0.002</v>
       </c>
       <c r="H12" t="n">
-        <v>372.894402335187</v>
+        <v>4.8884384979303</v>
       </c>
       <c r="I12" t="n">
-        <v>1721.762620415201</v>
+        <v>27.06474868351884</v>
       </c>
       <c r="J12" t="n">
-        <v>4.003924177611493</v>
+        <v>0.06788673516273602</v>
       </c>
       <c r="K12" t="n">
-        <v>2.612398967816962</v>
+        <v>2.790293819287251</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2019853225821379</v>
+        <v>0.175731586369983</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1307340120984004</v>
+        <v>0.1021361922958745</v>
       </c>
       <c r="F13" t="n">
-        <v>2.834829580127356</v>
+        <v>2.387806853687418</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H13" t="n">
-        <v>366.382401424986</v>
+        <v>5.011257518652267</v>
       </c>
       <c r="I13" t="n">
-        <v>1813.906063773498</v>
+        <v>28.51654402129866</v>
       </c>
       <c r="J13" t="n">
-        <v>3.740954275096111</v>
+        <v>0.06351750249680496</v>
       </c>
       <c r="K13" t="n">
-        <v>2.569018657828408</v>
+        <v>2.773600083382057</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2151759914931551</v>
+        <v>0.1680652615355053</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1508461547302989</v>
+        <v>0.0998738895302187</v>
       </c>
       <c r="F14" t="n">
-        <v>3.344886328351403</v>
+        <v>2.464611821015659</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H14" t="n">
-        <v>420.314162833587</v>
+        <v>5.418745801293722</v>
       </c>
       <c r="I14" t="n">
-        <v>1953.350649935113</v>
+        <v>32.24191455025323</v>
       </c>
       <c r="J14" t="n">
-        <v>3.782024143029835</v>
+        <v>0.06400814641100762</v>
       </c>
       <c r="K14" t="n">
-        <v>2.441011808041218</v>
+        <v>2.870856540458181</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2150772096139755</v>
+        <v>0.189229410150528</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1556133618574586</v>
+        <v>0.1278073957679924</v>
       </c>
       <c r="F15" t="n">
-        <v>3.616940674519399</v>
+        <v>3.080807623338579</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>445.8163320580769</v>
+        <v>6.579333416937649</v>
       </c>
       <c r="I15" t="n">
-        <v>2072.819955485922</v>
+        <v>34.7690848462928</v>
       </c>
       <c r="J15" t="n">
-        <v>3.658859998454521</v>
+        <v>0.07576874988840608</v>
       </c>
       <c r="K15" t="n">
-        <v>2.393493415826479</v>
+        <v>2.705625660438311</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2069058516357602</v>
+        <v>0.1738892475799274</v>
       </c>
       <c r="E16" t="n">
-        <v>0.150256269609743</v>
+        <v>0.1148813366927794</v>
       </c>
       <c r="F16" t="n">
-        <v>3.652380904429899</v>
+        <v>2.946880256657258</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>441.8609847593228</v>
+        <v>6.286981173014614</v>
       </c>
       <c r="I16" t="n">
-        <v>2135.565433582714</v>
+        <v>36.15508871602214</v>
       </c>
       <c r="J16" t="n">
-        <v>3.590484247439639</v>
+        <v>0.06690194985949706</v>
       </c>
       <c r="K16" t="n">
-        <v>2.300001600926214</v>
+        <v>2.639838030796089</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.206037107842932</v>
+        <v>0.1798298156871138</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1531062483657942</v>
+        <v>0.125151803399588</v>
       </c>
       <c r="F17" t="n">
-        <v>3.892570607736391</v>
+        <v>3.28888721743347</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>466.077005992272</v>
+        <v>6.975180767176227</v>
       </c>
       <c r="I17" t="n">
-        <v>2262.102253675468</v>
+        <v>38.78767678499075</v>
       </c>
       <c r="J17" t="n">
-        <v>3.719649470891374</v>
+        <v>0.07129939956317444</v>
       </c>
       <c r="K17" t="n">
-        <v>2.152082228616603</v>
+        <v>2.731893165862686</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2093621858134833</v>
+        <v>0.1708717472868291</v>
       </c>
       <c r="E18" t="n">
-        <v>0.159947322426826</v>
+        <v>0.1190512314922559</v>
       </c>
       <c r="F18" t="n">
-        <v>4.236826158463367</v>
+        <v>3.297376428366685</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>490.6328032422073</v>
+        <v>7.148605686711477</v>
       </c>
       <c r="I18" t="n">
-        <v>2343.464276205554</v>
+        <v>41.83608934899969</v>
       </c>
       <c r="J18" t="n">
-        <v>3.880943543285359</v>
+        <v>0.06764901263622927</v>
       </c>
       <c r="K18" t="n">
-        <v>2.025385196464771</v>
+        <v>2.556364796081964</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2011174880056351</v>
+        <v>0.1746007098195944</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1535649575297801</v>
+        <v>0.1254697996898083</v>
       </c>
       <c r="F19" t="n">
-        <v>4.229375093040591</v>
+        <v>3.553785373777175</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>497.7167371681098</v>
+        <v>7.637591563699626</v>
       </c>
       <c r="I19" t="n">
-        <v>2474.756134355478</v>
+        <v>43.74318736499491</v>
       </c>
       <c r="J19" t="n">
-        <v>3.77525515644381</v>
+        <v>0.06811586168470672</v>
       </c>
       <c r="K19" t="n">
-        <v>2.03894402386204</v>
+        <v>2.330223407508293</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1902772825425361</v>
+        <v>0.1696718068598802</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1447872422359372</v>
+        <v>0.1230241555598734</v>
       </c>
       <c r="F20" t="n">
-        <v>4.182833896388814</v>
+        <v>3.637306533798748</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H20" t="n">
-        <v>494.0484012342521</v>
+        <v>7.802786368144215</v>
       </c>
       <c r="I20" t="n">
-        <v>2596.465508822938</v>
+        <v>45.98752446001815</v>
       </c>
       <c r="J20" t="n">
-        <v>3.479229392771839</v>
+        <v>0.06358007542072557</v>
       </c>
       <c r="K20" t="n">
-        <v>1.952544574735014</v>
+        <v>2.232683500945971</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1852609552431625</v>
+        <v>0.1747190097596143</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1419237720114159</v>
+        <v>0.1308210847468279</v>
       </c>
       <c r="F21" t="n">
-        <v>4.274873017299599</v>
+        <v>3.980120010426977</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>506.0824491749424</v>
+        <v>8.382475897936551</v>
       </c>
       <c r="I21" t="n">
-        <v>2731.727516522241</v>
+        <v>47.97689678684369</v>
       </c>
       <c r="J21" t="n">
-        <v>3.296884438218762</v>
+        <v>0.06549012821831322</v>
       </c>
       <c r="K21" t="n">
-        <v>1.944269730865722</v>
+        <v>2.107938184256481</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1519193107930602</v>
+        <v>0.1778378572607078</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1086498878743388</v>
+        <v>0.1358908091617643</v>
       </c>
       <c r="F22" t="n">
-        <v>3.511008480016709</v>
+        <v>4.239579787384062</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>432.4825552328077</v>
+        <v>8.962644337772936</v>
       </c>
       <c r="I22" t="n">
-        <v>2846.791187868947</v>
+        <v>50.39784259565064</v>
       </c>
       <c r="J22" t="n">
-        <v>2.490132534510036</v>
+        <v>0.06567331184417234</v>
       </c>
       <c r="K22" t="n">
-        <v>1.928343768490618</v>
+        <v>2.028603484267691</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.142028693608067</v>
+        <v>0.1701132995714369</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1003796010647693</v>
+        <v>0.1298275374147106</v>
       </c>
       <c r="F23" t="n">
-        <v>3.410126966401879</v>
+        <v>4.222665538996976</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>425.980050971996</v>
+        <v>8.809766929608935</v>
       </c>
       <c r="I23" t="n">
-        <v>2999.253461751203</v>
+        <v>51.78764359872631</v>
       </c>
       <c r="J23" t="n">
-        <v>2.295741985857672</v>
+        <v>0.06516191669144014</v>
       </c>
       <c r="K23" t="n">
-        <v>1.866755586915355</v>
+        <v>1.942216420625014</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1366024241657811</v>
+        <v>0.1863182103657641</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09663031417345613</v>
+        <v>0.1486477571419569</v>
       </c>
       <c r="F24" t="n">
-        <v>3.417443417222911</v>
+        <v>4.946003947943304</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>436.4368663507778</v>
+        <v>10.21590385811427</v>
       </c>
       <c r="I24" t="n">
-        <v>3194.942322700781</v>
+        <v>54.83040996400337</v>
       </c>
       <c r="J24" t="n">
-        <v>2.172450860342993</v>
+        <v>0.07113533858959692</v>
       </c>
       <c r="K24" t="n">
-        <v>1.906156318846348</v>
+        <v>1.868953081065527</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1405594337374323</v>
+        <v>0.1714061032786756</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1021915513149961</v>
+        <v>0.1344153043179021</v>
       </c>
       <c r="F25" t="n">
-        <v>3.663466025824729</v>
+        <v>4.633749691658236</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>462.8939063340126</v>
+        <v>9.757655261024643</v>
       </c>
       <c r="I25" t="n">
-        <v>3293.225463605006</v>
+        <v>56.92711679677149</v>
       </c>
       <c r="J25" t="n">
-        <v>2.14703554492774</v>
+        <v>0.06694816713498362</v>
       </c>
       <c r="K25" t="n">
-        <v>1.91380710115703</v>
+        <v>1.840631994946188</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1358033700147729</v>
+        <v>0.1750355112858455</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09887189010087416</v>
+        <v>0.1397806186057534</v>
       </c>
       <c r="F26" t="n">
-        <v>3.677171083622493</v>
+        <v>4.964857300067334</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>461.1905521878931</v>
+        <v>10.42023207959173</v>
       </c>
       <c r="I26" t="n">
-        <v>3396.016992345067</v>
+        <v>59.53210296038012</v>
       </c>
       <c r="J26" t="n">
-        <v>2.082920361615687</v>
+        <v>0.06614352695464189</v>
       </c>
       <c r="K26" t="n">
-        <v>1.854809118454482</v>
+        <v>1.767252564395192</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1332027085563397</v>
+        <v>0.1767004621056756</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09767822939881265</v>
+        <v>0.1429586777657443</v>
       </c>
       <c r="F27" t="n">
-        <v>3.749603420381637</v>
+        <v>5.236844036625574</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>469.3637949481593</v>
+        <v>10.89124665793424</v>
       </c>
       <c r="I27" t="n">
-        <v>3523.680562018274</v>
+        <v>61.63677518523258</v>
       </c>
       <c r="J27" t="n">
-        <v>2.071786975938257</v>
+        <v>0.06796702374130593</v>
       </c>
       <c r="K27" t="n">
-        <v>1.785051101279934</v>
+        <v>1.723871423516526</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.129373052194818</v>
+        <v>0.1732553812193149</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09482436378985037</v>
+        <v>0.1404480550772242</v>
       </c>
       <c r="F28" t="n">
-        <v>3.744658861672339</v>
+        <v>5.280996703874451</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>471.5351704146756</v>
+        <v>10.93091324724495</v>
       </c>
       <c r="I28" t="n">
-        <v>3644.77116690892</v>
+        <v>63.09133471247323</v>
       </c>
       <c r="J28" t="n">
-        <v>1.998278502544533</v>
+        <v>0.06555598567619723</v>
       </c>
       <c r="K28" t="n">
-        <v>1.723990883161243</v>
+        <v>1.656345173559502</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1265472854439767</v>
+        <v>0.1702329244989447</v>
       </c>
       <c r="E29" t="n">
-        <v>0.09320939557542629</v>
+        <v>0.138562425434019</v>
       </c>
       <c r="F29" t="n">
-        <v>3.795899678802283</v>
+        <v>5.375126048691576</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>476.63842698691</v>
+        <v>11.10358752769292</v>
       </c>
       <c r="I29" t="n">
-        <v>3766.484799058931</v>
+        <v>65.22585193419354</v>
       </c>
       <c r="J29" t="n">
-        <v>1.822315396749286</v>
+        <v>0.0634067894464018</v>
       </c>
       <c r="K29" t="n">
-        <v>1.664013653219596</v>
+        <v>1.638857066983883</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1265270299361721</v>
+        <v>0.1562234214365246</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09441405309559003</v>
+        <v>0.1252022236952203</v>
       </c>
       <c r="F30" t="n">
-        <v>3.940059202991015</v>
+        <v>5.036021585604853</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>488.5957307614036</v>
+        <v>10.42281239708319</v>
       </c>
       <c r="I30" t="n">
-        <v>3861.591716867779</v>
+        <v>66.7173481494777</v>
       </c>
       <c r="J30" t="n">
-        <v>1.826611159017973</v>
+        <v>0.05967933756765446</v>
       </c>
       <c r="K30" t="n">
-        <v>1.587831069328213</v>
+        <v>1.540690766967645</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1261083654081012</v>
+        <v>0.1510373294698574</v>
       </c>
       <c r="E31" t="n">
-        <v>0.09489794988696187</v>
+        <v>0.1207172340937808</v>
       </c>
       <c r="F31" t="n">
-        <v>4.040585916668949</v>
+        <v>4.981426595017587</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>503.1048221317911</v>
+        <v>10.27659950292629</v>
       </c>
       <c r="I31" t="n">
-        <v>3989.464303210069</v>
+        <v>68.04012980762613</v>
       </c>
       <c r="J31" t="n">
-        <v>1.831954074746186</v>
+        <v>0.05734889566913642</v>
       </c>
       <c r="K31" t="n">
-        <v>1.567747518035267</v>
+        <v>1.535645355348145</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1243778106823422</v>
+        <v>0.1516738079758333</v>
       </c>
       <c r="E32" t="n">
-        <v>0.09418394208518155</v>
+        <v>0.1224211806646551</v>
       </c>
       <c r="F32" t="n">
-        <v>4.119306881200327</v>
+        <v>5.184963605572445</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>512.522213182429</v>
+        <v>10.70956702177532</v>
       </c>
       <c r="I32" t="n">
-        <v>4120.688492350118</v>
+        <v>70.60920514029499</v>
       </c>
       <c r="J32" t="n">
-        <v>1.708714207771416</v>
+        <v>0.05780863962212959</v>
       </c>
       <c r="K32" t="n">
-        <v>1.501264436918065</v>
+        <v>1.488797037449247</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1205288020821648</v>
+        <v>0.1376168293479986</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09121309548490353</v>
+        <v>0.1088707236595984</v>
       </c>
       <c r="F33" t="n">
-        <v>4.111407026205714</v>
+        <v>4.787320788413134</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>511.4412066748536</v>
+        <v>10.07824244714812</v>
       </c>
       <c r="I33" t="n">
-        <v>4243.311124308717</v>
+        <v>73.23408404987129</v>
       </c>
       <c r="J33" t="n">
-        <v>1.691465242853456</v>
+        <v>0.04989681981400761</v>
       </c>
       <c r="K33" t="n">
-        <v>1.418814427042176</v>
+        <v>1.400490869902281</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1192626179099352</v>
+        <v>0.1331098127817443</v>
       </c>
       <c r="E34" t="n">
-        <v>0.09066724836155637</v>
+        <v>0.1049640274824502</v>
       </c>
       <c r="F34" t="n">
-        <v>4.170696857341265</v>
+        <v>4.72929823653146</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>515.4175092230194</v>
+        <v>10.05863435175766</v>
       </c>
       <c r="I34" t="n">
-        <v>4321.702124736625</v>
+        <v>75.56643752666432</v>
       </c>
       <c r="J34" t="n">
-        <v>1.660390594893963</v>
+        <v>0.04781987177008215</v>
       </c>
       <c r="K34" t="n">
-        <v>1.38263601460429</v>
+        <v>1.340260778898987</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1200355183551893</v>
+        <v>0.1364747120997007</v>
       </c>
       <c r="E35" t="n">
-        <v>0.09236367930975509</v>
+        <v>0.1093198288323958</v>
       </c>
       <c r="F35" t="n">
-        <v>4.337822222733495</v>
+        <v>5.025788943973066</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>536.7334876235832</v>
+        <v>10.7555958940999</v>
       </c>
       <c r="I35" t="n">
-        <v>4471.455573969113</v>
+        <v>78.8101746369135</v>
       </c>
       <c r="J35" t="n">
-        <v>1.763759890837507</v>
+        <v>0.05107270800997977</v>
       </c>
       <c r="K35" t="n">
-        <v>1.351084176364486</v>
+        <v>1.275757087929616</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1146288294000573</v>
+        <v>0.1223469071727016</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08763580590615649</v>
+        <v>0.09558919092796681</v>
       </c>
       <c r="F36" t="n">
-        <v>4.246609477665912</v>
+        <v>4.572397212590091</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>523.7566191501485</v>
+        <v>9.869989647396904</v>
       </c>
       <c r="I36" t="n">
-        <v>4569.152645903986</v>
+        <v>80.67216307695213</v>
       </c>
       <c r="J36" t="n">
-        <v>1.605832451695726</v>
+        <v>0.04470954274268862</v>
       </c>
       <c r="K36" t="n">
-        <v>1.331771396104315</v>
+        <v>1.250863946408975</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.114848349437289</v>
+        <v>0.1293040450043632</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08850455031339888</v>
+        <v>0.1033904749152075</v>
       </c>
       <c r="F37" t="n">
-        <v>4.359597068637579</v>
+        <v>4.989819795554666</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>535.4027718735236</v>
+        <v>10.72023337915683</v>
       </c>
       <c r="I37" t="n">
-        <v>4661.82382678361</v>
+        <v>82.90717725648173</v>
       </c>
       <c r="J37" t="n">
-        <v>1.615690199927038</v>
+        <v>0.04781902177802135</v>
       </c>
       <c r="K37" t="n">
-        <v>1.31849363591426</v>
+        <v>1.230859493258122</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.11564917741161</v>
+        <v>0.1283135879113764</v>
       </c>
       <c r="E38" t="n">
-        <v>0.09008990508246573</v>
+        <v>0.1031203390070808</v>
       </c>
       <c r="F38" t="n">
-        <v>4.524744520200595</v>
+        <v>5.093173508459195</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>553.3420844740365</v>
+        <v>10.95546106543624</v>
       </c>
       <c r="I38" t="n">
-        <v>4784.660789281901</v>
+        <v>85.38036574117905</v>
       </c>
       <c r="J38" t="n">
-        <v>1.664823246821699</v>
+        <v>0.04779846018284575</v>
       </c>
       <c r="K38" t="n">
-        <v>1.240158400622891</v>
+        <v>1.208248342730408</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1185169187405238</v>
+        <v>0.1255833968440966</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09375615803098791</v>
+        <v>0.1010211327105038</v>
       </c>
       <c r="F39" t="n">
-        <v>4.786481325465926</v>
+        <v>5.112859146903373</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>584.5904308302471</v>
+        <v>10.91683020568811</v>
       </c>
       <c r="I39" t="n">
-        <v>4932.548340293305</v>
+        <v>86.92892914212717</v>
       </c>
       <c r="J39" t="n">
-        <v>1.788409989817402</v>
+        <v>0.04726848964341904</v>
       </c>
       <c r="K39" t="n">
-        <v>1.193608247017479</v>
+        <v>1.17660587484867</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1203244636896338</v>
+        <v>0.12039449162844</v>
       </c>
       <c r="E40" t="n">
-        <v>0.09615755335143705</v>
+        <v>0.09622950513471584</v>
       </c>
       <c r="F40" t="n">
-        <v>4.978893123108736</v>
+        <v>4.982187416479928</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>610.1920656787864</v>
+        <v>10.65090174542406</v>
       </c>
       <c r="I40" t="n">
-        <v>5071.221985686321</v>
+        <v>88.46668648508228</v>
       </c>
       <c r="J40" t="n">
-        <v>1.851542114469723</v>
+        <v>0.04531452522257091</v>
       </c>
       <c r="K40" t="n">
-        <v>1.162980220341784</v>
+        <v>1.141424383478388</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.113997027418318</v>
+        <v>0.118398379991163</v>
       </c>
       <c r="E41" t="n">
-        <v>0.09030710836533173</v>
+        <v>0.0948261441620496</v>
       </c>
       <c r="F41" t="n">
-        <v>4.812047992369501</v>
+        <v>5.022789558423351</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>590.0193912208965</v>
+        <v>10.72465217291278</v>
       </c>
       <c r="I41" t="n">
-        <v>5175.743653874322</v>
+        <v>90.58107191764991</v>
       </c>
       <c r="J41" t="n">
-        <v>1.742884251095251</v>
+        <v>0.04524985112674351</v>
       </c>
       <c r="K41" t="n">
-        <v>1.124216685430463</v>
+        <v>1.122854526749683</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1168762596406983</v>
+        <v>0.115769414608634</v>
       </c>
       <c r="E42" t="n">
-        <v>0.09387824556884139</v>
+        <v>0.09274257644740047</v>
       </c>
       <c r="F42" t="n">
-        <v>5.082015311214302</v>
+        <v>5.027586236461065</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>614.1526489755006</v>
+        <v>10.68044323178779</v>
       </c>
       <c r="I42" t="n">
-        <v>5254.725389600355</v>
+        <v>92.25617377347656</v>
       </c>
       <c r="J42" t="n">
-        <v>1.758360445111801</v>
+        <v>0.04397591802240389</v>
       </c>
       <c r="K42" t="n">
-        <v>1.102328419504835</v>
+        <v>1.094959332343793</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1117697360686736</v>
+        <v>0.1178419295909922</v>
       </c>
       <c r="E43" t="n">
-        <v>0.089110800764303</v>
+        <v>0.09533789718259911</v>
       </c>
       <c r="F43" t="n">
-        <v>4.932700260065389</v>
+        <v>5.236480620559457</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>605.0377515837699</v>
+        <v>11.09683399555101</v>
       </c>
       <c r="I43" t="n">
-        <v>5413.25203820847</v>
+        <v>94.16711041703148</v>
       </c>
       <c r="J43" t="n">
-        <v>1.691498639240828</v>
+        <v>0.04506351121852373</v>
       </c>
       <c r="K43" t="n">
-        <v>1.089845956461364</v>
+        <v>1.084243217811965</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1137802354582049</v>
+        <v>0.1171160633472289</v>
       </c>
       <c r="E44" t="n">
-        <v>0.09173496768353329</v>
+        <v>0.09515377636581668</v>
       </c>
       <c r="F44" t="n">
-        <v>5.161209045912811</v>
+        <v>5.332598715532223</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>627.098165386393</v>
+        <v>11.25661508875681</v>
       </c>
       <c r="I44" t="n">
-        <v>5511.485917224581</v>
+        <v>96.1150397907663</v>
       </c>
       <c r="J44" t="n">
-        <v>1.728356824745245</v>
+        <v>0.04506194937414686</v>
       </c>
       <c r="K44" t="n">
-        <v>1.073182950068007</v>
+        <v>1.072879655498824</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1074872900152832</v>
+        <v>0.1215586271871556</v>
       </c>
       <c r="E45" t="n">
-        <v>0.08582436016128525</v>
+        <v>0.1002372346431545</v>
       </c>
       <c r="F45" t="n">
-        <v>4.9618076012671</v>
+        <v>5.701251779699398</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>610.83073116961</v>
+        <v>11.96515610829346</v>
       </c>
       <c r="I45" t="n">
-        <v>5682.818229790315</v>
+        <v>98.43115528008981</v>
       </c>
       <c r="J45" t="n">
-        <v>1.628968338845764</v>
+        <v>0.04787049724027319</v>
       </c>
       <c r="K45" t="n">
-        <v>1.053294548149652</v>
+        <v>1.053397444760216</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1020295840188423</v>
+        <v>0.1182816598929944</v>
       </c>
       <c r="E46" t="n">
-        <v>0.08064933601929103</v>
+        <v>0.09728836608092284</v>
       </c>
       <c r="F46" t="n">
-        <v>4.772142213737801</v>
+        <v>5.63425925211317</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>590.1995516409725</v>
+        <v>11.85996797295131</v>
       </c>
       <c r="I46" t="n">
-        <v>5784.59235442906</v>
+        <v>100.2688665654561</v>
       </c>
       <c r="J46" t="n">
-        <v>1.527722933948716</v>
+        <v>0.04624667216604619</v>
       </c>
       <c r="K46" t="n">
-        <v>1.03571279285526</v>
+        <v>1.03745385910538</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1036068017459348</v>
+        <v>0.1212951430931017</v>
       </c>
       <c r="E47" t="n">
-        <v>0.08276044829816587</v>
+        <v>0.1008601464208482</v>
       </c>
       <c r="F47" t="n">
-        <v>4.970020392560461</v>
+        <v>5.935657589697368</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>609.6677492041615</v>
+        <v>12.34430503726941</v>
       </c>
       <c r="I47" t="n">
-        <v>5884.437497638352</v>
+        <v>101.7708106234261</v>
       </c>
       <c r="J47" t="n">
-        <v>1.56829131254944</v>
+        <v>0.0480334934313023</v>
       </c>
       <c r="K47" t="n">
-        <v>1.020801852291942</v>
+        <v>1.021710750376712</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1012738812400337</v>
+        <v>0.1228520545628626</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08084828763185259</v>
+        <v>0.1029168739847459</v>
       </c>
       <c r="F48" t="n">
-        <v>4.958185460003986</v>
+        <v>6.162575457065072</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>602.3146729435346</v>
+        <v>12.6843811612653</v>
       </c>
       <c r="I48" t="n">
-        <v>5947.384118872291</v>
+        <v>103.2492391470326</v>
       </c>
       <c r="J48" t="n">
-        <v>1.510734175521866</v>
+        <v>0.0488472571017978</v>
       </c>
       <c r="K48" t="n">
-        <v>1.008264640885453</v>
+        <v>1.010373464728372</v>
       </c>
     </row>
     <row r="49">
@@ -2136,28 +2136,28 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1022260327650234</v>
+        <v>0.1248915760800551</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08218643528209979</v>
+        <v>0.1053579059032705</v>
       </c>
       <c r="F49" t="n">
-        <v>5.101201900493942</v>
+        <v>6.393656437820223</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>619.2086592210894</v>
+        <v>13.11341883830757</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.250217705322</v>
+        <v>104.9984254334489</v>
       </c>
       <c r="J49" t="n">
-        <v>1.561599279426492</v>
+        <v>0.04993911090901088</v>
       </c>
       <c r="K49" t="n">
-        <v>1.003593779634436</v>
+        <v>1.004489866792857</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,25 +491,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5165489478689989</v>
+        <v>0.4925408876868616</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03309789573799771</v>
+        <v>-0.0149182246262769</v>
       </c>
       <c r="F2" t="n">
-        <v>1.068461730700772</v>
+        <v>0.9706021149994218</v>
       </c>
       <c r="G2" t="n">
-        <v>0.435</v>
+        <v>0.525</v>
       </c>
       <c r="H2" t="n">
-        <v>2.444897096111021</v>
+        <v>116.788271326476</v>
       </c>
       <c r="I2" t="n">
-        <v>4.733137307117441</v>
+        <v>237.113860485681</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1387412910586835</v>
+        <v>5.359957295715329</v>
       </c>
       <c r="K2" t="n">
         <v>9.145636738102082</v>
@@ -526,25 +526,25 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4259668859313568</v>
+        <v>0.3970233575455657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1389503288970352</v>
+        <v>0.09553503631834859</v>
       </c>
       <c r="F3" t="n">
-        <v>1.484119558581491</v>
+        <v>1.316878066551535</v>
       </c>
       <c r="G3" t="n">
-        <v>0.121</v>
+        <v>0.172</v>
       </c>
       <c r="H3" t="n">
-        <v>3.186719447168445</v>
+        <v>154.5841489470177</v>
       </c>
       <c r="I3" t="n">
-        <v>7.481143610965981</v>
+        <v>389.3578199093144</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1075146359929333</v>
+        <v>4.710835345943221</v>
       </c>
       <c r="K3" t="n">
         <v>7.066033920197936</v>
@@ -561,25 +561,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.36741205445111</v>
+        <v>0.356658965838565</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1414877881836492</v>
+        <v>0.1268943107809096</v>
       </c>
       <c r="F4" t="n">
-        <v>1.626262023647114</v>
+        <v>1.552279508565265</v>
       </c>
       <c r="G4" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="H4" t="n">
-        <v>3.589090543528475</v>
+        <v>187.1540776890202</v>
       </c>
       <c r="I4" t="n">
-        <v>9.768570464815983</v>
+        <v>524.7423887101495</v>
       </c>
       <c r="J4" t="n">
-        <v>0.127760008516781</v>
+        <v>5.967576259658116</v>
       </c>
       <c r="K4" t="n">
         <v>5.906324511842218</v>
@@ -596,25 +596,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2974187109294179</v>
+        <v>0.2892518523574867</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1125288980161068</v>
+        <v>0.1022128661357727</v>
       </c>
       <c r="F5" t="n">
-        <v>1.608626815306845</v>
+        <v>1.546478935758402</v>
       </c>
       <c r="G5" t="n">
-        <v>0.083</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81811964404275</v>
+        <v>196.0994682513464</v>
       </c>
       <c r="I5" t="n">
-        <v>12.83752334246667</v>
+        <v>677.9540620157787</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1129046677733935</v>
+        <v>5.083107668153946</v>
       </c>
       <c r="K5" t="n">
         <v>6.062995790074879</v>
@@ -631,25 +631,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.249875983412775</v>
+        <v>0.2456088688191881</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09360014662376992</v>
+        <v>0.08844404982318566</v>
       </c>
       <c r="F6" t="n">
-        <v>1.598941900084934</v>
+        <v>1.562747123613174</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="H6" t="n">
-        <v>3.813291732885132</v>
+        <v>203.9583031954551</v>
       </c>
       <c r="I6" t="n">
-        <v>15.26073726975946</v>
+        <v>830.419130123533</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09806913748105053</v>
+        <v>5.185312301894066</v>
       </c>
       <c r="K6" t="n">
         <v>3.372238329751428</v>
@@ -666,25 +666,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1693782491600118</v>
+        <v>0.1681260770887759</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02105293651001383</v>
+        <v>0.01957716228320017</v>
       </c>
       <c r="F7" t="n">
-        <v>1.141937583908502</v>
+        <v>1.131789332213051</v>
       </c>
       <c r="G7" t="n">
-        <v>0.31</v>
+        <v>0.321</v>
       </c>
       <c r="H7" t="n">
-        <v>2.888125564650369</v>
+        <v>156.7245605671517</v>
       </c>
       <c r="I7" t="n">
-        <v>17.05133675057625</v>
+        <v>932.1847228041613</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05254961479562898</v>
+        <v>3.233123149939415</v>
       </c>
       <c r="K7" t="n">
         <v>3.75034946795072</v>
@@ -701,25 +701,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.168227876094482</v>
+        <v>0.1725104632447115</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04220179671485791</v>
+        <v>0.04713326070603141</v>
       </c>
       <c r="F8" t="n">
-        <v>1.334865584350482</v>
+        <v>1.375931666616109</v>
       </c>
       <c r="G8" t="n">
-        <v>0.167</v>
+        <v>0.118</v>
       </c>
       <c r="H8" t="n">
-        <v>3.205177317793258</v>
+        <v>180.984819443416</v>
       </c>
       <c r="I8" t="n">
-        <v>19.05259337633872</v>
+        <v>1049.123722928524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05829159907333734</v>
+        <v>3.38378656325168</v>
       </c>
       <c r="K8" t="n">
         <v>3.535358492741626</v>
@@ -736,25 +736,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1517964992571969</v>
+        <v>0.1477698430525909</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04019077547524919</v>
+        <v>0.03563429608582658</v>
       </c>
       <c r="F9" t="n">
-        <v>1.360113927075754</v>
+        <v>1.31777876908549</v>
       </c>
       <c r="G9" t="n">
-        <v>0.155</v>
+        <v>0.145</v>
       </c>
       <c r="H9" t="n">
-        <v>3.167325878216349</v>
+        <v>171.355457598894</v>
       </c>
       <c r="I9" t="n">
-        <v>20.86560555556542</v>
+        <v>1159.610473010444</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05028892640603198</v>
+        <v>2.587354522628796</v>
       </c>
       <c r="K9" t="n">
         <v>3.860154330167111</v>
@@ -771,25 +771,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1752176576077353</v>
+        <v>0.160938677631404</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07702928351341809</v>
+        <v>0.0610504249684759</v>
       </c>
       <c r="F10" t="n">
-        <v>1.784505133361571</v>
+        <v>1.611187235144557</v>
       </c>
       <c r="G10" t="n">
         <v>0.038</v>
       </c>
       <c r="H10" t="n">
-        <v>3.905079307182867</v>
+        <v>199.2998804240868</v>
       </c>
       <c r="I10" t="n">
-        <v>22.28701924508817</v>
+        <v>1238.359127571192</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05877437848956074</v>
+        <v>2.777751313156684</v>
       </c>
       <c r="K10" t="n">
         <v>3.485812317750533</v>
@@ -806,25 +806,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1903949125714409</v>
+        <v>0.189661878159923</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1042667117811686</v>
+        <v>0.1034556949854466</v>
       </c>
       <c r="F11" t="n">
-        <v>2.210598977158073</v>
+        <v>2.200095992836829</v>
       </c>
       <c r="G11" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="H11" t="n">
-        <v>4.775101986962683</v>
+        <v>272.6348351730873</v>
       </c>
       <c r="I11" t="n">
-        <v>25.07998728784807</v>
+        <v>1437.47830517212</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0726045339019856</v>
+        <v>3.947597993547647</v>
       </c>
       <c r="K11" t="n">
         <v>3.026876285456252</v>
@@ -841,25 +841,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1806201326712163</v>
+        <v>0.1683130747881656</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1018336069665255</v>
+        <v>0.08834317813318149</v>
       </c>
       <c r="F12" t="n">
-        <v>2.292525670547022</v>
+        <v>2.104705418269108</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8884384979303</v>
+        <v>259.0013212245683</v>
       </c>
       <c r="I12" t="n">
-        <v>27.06474868351884</v>
+        <v>1538.806902259616</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06788673516273602</v>
+        <v>3.44703099723679</v>
       </c>
       <c r="K12" t="n">
         <v>2.790293819287251</v>
@@ -876,25 +876,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.175731586369983</v>
+        <v>0.1556790590251084</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1021361922958745</v>
+        <v>0.08029326072377885</v>
       </c>
       <c r="F13" t="n">
-        <v>2.387806853687418</v>
+        <v>2.065097969816984</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="H13" t="n">
-        <v>5.011257518652267</v>
+        <v>253.1352608338389</v>
       </c>
       <c r="I13" t="n">
-        <v>28.51654402129866</v>
+        <v>1626.007135571217</v>
       </c>
       <c r="J13" t="n">
-        <v>0.06351750249680496</v>
+        <v>3.079566442377794</v>
       </c>
       <c r="K13" t="n">
         <v>2.773600083382057</v>
@@ -911,25 +911,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1680652615355053</v>
+        <v>0.1559241099348409</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0998738895302187</v>
+        <v>0.08673756156884427</v>
       </c>
       <c r="F14" t="n">
-        <v>2.464611821015659</v>
+        <v>2.253676670066019</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="H14" t="n">
-        <v>5.418745801293722</v>
+        <v>291.4920339690231</v>
       </c>
       <c r="I14" t="n">
-        <v>32.24191455025323</v>
+        <v>1869.448118644606</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06400814641100762</v>
+        <v>3.170858811199212</v>
       </c>
       <c r="K14" t="n">
         <v>2.870856540458181</v>
@@ -946,25 +946,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.189229410150528</v>
+        <v>0.1728469102031027</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1278073957679924</v>
+        <v>0.1101837973397015</v>
       </c>
       <c r="F15" t="n">
-        <v>3.080807623338579</v>
+        <v>2.758351800682005</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>6.579333416937649</v>
+        <v>346.8482057026886</v>
       </c>
       <c r="I15" t="n">
-        <v>34.7690848462928</v>
+        <v>2006.678657403402</v>
       </c>
       <c r="J15" t="n">
-        <v>0.07576874988840608</v>
+        <v>3.711231175026501</v>
       </c>
       <c r="K15" t="n">
         <v>2.705625660438311</v>
@@ -981,25 +981,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1738892475799274</v>
+        <v>0.1605148524164015</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1148813366927794</v>
+        <v>0.1005516275890016</v>
       </c>
       <c r="F16" t="n">
-        <v>2.946880256657258</v>
+        <v>2.676888257401644</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>6.286981173014614</v>
+        <v>337.2639928438506</v>
       </c>
       <c r="I16" t="n">
-        <v>36.15508871602214</v>
+        <v>2101.138852677216</v>
       </c>
       <c r="J16" t="n">
-        <v>0.06690194985949706</v>
+        <v>3.297910718256711</v>
       </c>
       <c r="K16" t="n">
         <v>2.639838030796089</v>
@@ -1016,25 +1016,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1798298156871138</v>
+        <v>0.1655664498120034</v>
       </c>
       <c r="E17" t="n">
-        <v>0.125151803399588</v>
+        <v>0.109937546466137</v>
       </c>
       <c r="F17" t="n">
-        <v>3.28888721743347</v>
+        <v>2.976266650137117</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>6.975180767176227</v>
+        <v>371.028394383361</v>
       </c>
       <c r="I17" t="n">
-        <v>38.78767678499075</v>
+        <v>2240.963642118645</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07129939956317444</v>
+        <v>3.546265171548783</v>
       </c>
       <c r="K17" t="n">
         <v>2.731893165862686</v>
@@ -1051,25 +1051,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1708717472868291</v>
+        <v>0.1594273508962541</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1190512314922559</v>
+        <v>0.10689156032727</v>
       </c>
       <c r="F18" t="n">
-        <v>3.297376428366685</v>
+        <v>3.034642653505175</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>7.148605686711477</v>
+        <v>389.0544489102685</v>
       </c>
       <c r="I18" t="n">
-        <v>41.83608934899969</v>
+        <v>2440.324365443682</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06764901263622927</v>
+        <v>3.302255441161214</v>
       </c>
       <c r="K18" t="n">
         <v>2.556364796081964</v>
@@ -1086,25 +1086,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1746007098195944</v>
+        <v>0.1576762124348407</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1254697996898083</v>
+        <v>0.1075378917464382</v>
       </c>
       <c r="F19" t="n">
-        <v>3.553785373777175</v>
+        <v>3.144824363280146</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>7.637591563699626</v>
+        <v>395.6873803563738</v>
       </c>
       <c r="I19" t="n">
-        <v>43.74318736499491</v>
+        <v>2509.493183823722</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06811586168470672</v>
+        <v>3.16157645007891</v>
       </c>
       <c r="K19" t="n">
         <v>2.330223407508293</v>
@@ -1121,25 +1121,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1696718068598802</v>
+        <v>0.1510311715867109</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1230241555598734</v>
+        <v>0.1033362935859645</v>
       </c>
       <c r="F20" t="n">
-        <v>3.637306533798748</v>
+        <v>3.166611970038938</v>
       </c>
       <c r="G20" t="n">
         <v>0.002</v>
       </c>
       <c r="H20" t="n">
-        <v>7.802786368144215</v>
+        <v>398.3174512257812</v>
       </c>
       <c r="I20" t="n">
-        <v>45.98752446001815</v>
+        <v>2637.31948207193</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06358007542072557</v>
+        <v>2.846522369821444</v>
       </c>
       <c r="K20" t="n">
         <v>2.232683500945971</v>
@@ -1156,25 +1156,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1747190097596143</v>
+        <v>0.1530262536691974</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1308210847468279</v>
+        <v>0.1079744586516016</v>
       </c>
       <c r="F21" t="n">
-        <v>3.980120010426977</v>
+        <v>3.396673841950801</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>8.382475897936551</v>
+        <v>422.3620976787218</v>
       </c>
       <c r="I21" t="n">
-        <v>47.97689678684369</v>
+        <v>2760.062979727373</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06549012821831322</v>
+        <v>2.840168227951631</v>
       </c>
       <c r="K21" t="n">
         <v>2.107938184256481</v>
@@ -1191,25 +1191,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1778378572607078</v>
+        <v>0.1532354754980822</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1358908091617643</v>
+        <v>0.1100332038398212</v>
       </c>
       <c r="F22" t="n">
-        <v>4.239579787384062</v>
+        <v>3.546930974144287</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>8.962644337772936</v>
+        <v>440.0112574103838</v>
       </c>
       <c r="I22" t="n">
-        <v>50.39784259565064</v>
+        <v>2871.471217615602</v>
       </c>
       <c r="J22" t="n">
-        <v>0.06567331184417234</v>
+        <v>2.833777676689714</v>
       </c>
       <c r="K22" t="n">
         <v>2.028603484267691</v>
@@ -1226,25 +1226,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1701132995714369</v>
+        <v>0.1453323851435263</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1298275374147106</v>
+        <v>0.1038436659757364</v>
       </c>
       <c r="F23" t="n">
-        <v>4.222665538996976</v>
+        <v>3.502937378128461</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>8.809766929608935</v>
+        <v>428.7638148078412</v>
       </c>
       <c r="I23" t="n">
-        <v>51.78764359872631</v>
+        <v>2950.228982923563</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06516191669144014</v>
+        <v>2.740696936599851</v>
       </c>
       <c r="K23" t="n">
         <v>1.942216420625014</v>
@@ -1261,25 +1261,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1863182103657641</v>
+        <v>0.162248237343661</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1486477571419569</v>
+        <v>0.1234634335169786</v>
       </c>
       <c r="F24" t="n">
-        <v>4.946003947943304</v>
+        <v>4.183294005268137</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>10.21590385811427</v>
+        <v>508.257297814339</v>
       </c>
       <c r="I24" t="n">
-        <v>54.83040996400337</v>
+        <v>3132.590566995127</v>
       </c>
       <c r="J24" t="n">
-        <v>0.07113533858959692</v>
+        <v>2.978442996777887</v>
       </c>
       <c r="K24" t="n">
         <v>1.868953081065527</v>
@@ -1296,25 +1296,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1714061032786756</v>
+        <v>0.1569135331589881</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1344153043179021</v>
+        <v>0.1192757444607286</v>
       </c>
       <c r="F25" t="n">
-        <v>4.633749691658236</v>
+        <v>4.169042299933113</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>9.757655261024643</v>
+        <v>509.9235183857994</v>
       </c>
       <c r="I25" t="n">
-        <v>56.92711679677149</v>
+        <v>3249.710258382456</v>
       </c>
       <c r="J25" t="n">
-        <v>0.06694816713498362</v>
+        <v>2.861502134773557</v>
       </c>
       <c r="K25" t="n">
         <v>1.840631994946188</v>
@@ -1331,25 +1331,25 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1750355112858455</v>
+        <v>0.1616065009425485</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1397806186057534</v>
+        <v>0.1257777189315462</v>
       </c>
       <c r="F26" t="n">
-        <v>4.964857300067334</v>
+        <v>4.51052176132928</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>10.42023207959173</v>
+        <v>542.5791391529224</v>
       </c>
       <c r="I26" t="n">
-        <v>59.53210296038012</v>
+        <v>3357.409114041832</v>
       </c>
       <c r="J26" t="n">
-        <v>0.06614352695464189</v>
+        <v>2.831863585982722</v>
       </c>
       <c r="K26" t="n">
         <v>1.767252564395192</v>
@@ -1366,25 +1366,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1767004621056756</v>
+        <v>0.1611367856924726</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1429586777657443</v>
+        <v>0.1267571457618363</v>
       </c>
       <c r="F27" t="n">
-        <v>5.236844036625574</v>
+        <v>4.6869829357602</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>10.89124665793424</v>
+        <v>558.3611995045231</v>
       </c>
       <c r="I27" t="n">
-        <v>61.63677518523258</v>
+        <v>3465.138001264018</v>
       </c>
       <c r="J27" t="n">
-        <v>0.06796702374130593</v>
+        <v>2.807130603273303</v>
       </c>
       <c r="K27" t="n">
         <v>1.723871423516526</v>
@@ -1401,25 +1401,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1732553812193149</v>
+        <v>0.1585398479594011</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1404480550772242</v>
+        <v>0.1251485720847741</v>
       </c>
       <c r="F28" t="n">
-        <v>5.280996703874451</v>
+        <v>4.747942203666165</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>10.93091324724495</v>
+        <v>561.529282412726</v>
       </c>
       <c r="I28" t="n">
-        <v>63.09133471247323</v>
+        <v>3541.881045303655</v>
       </c>
       <c r="J28" t="n">
-        <v>0.06555598567619723</v>
+        <v>2.732309827059296</v>
       </c>
       <c r="K28" t="n">
         <v>1.656345173559502</v>
@@ -1436,25 +1436,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1702329244989447</v>
+        <v>0.1573926571234671</v>
       </c>
       <c r="E29" t="n">
-        <v>0.138562425434019</v>
+        <v>0.1252320715174927</v>
       </c>
       <c r="F29" t="n">
-        <v>5.375126048691576</v>
+        <v>4.893961168860929</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>11.10358752769292</v>
+        <v>579.4287909260013</v>
       </c>
       <c r="I29" t="n">
-        <v>65.22585193419354</v>
+        <v>3681.422002244149</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0634067894464018</v>
+        <v>2.600914928441721</v>
       </c>
       <c r="K29" t="n">
         <v>1.638857066983883</v>
@@ -1471,25 +1471,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1562234214365246</v>
+        <v>0.1497199810106986</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1252022236952203</v>
+        <v>0.1184596861949154</v>
       </c>
       <c r="F30" t="n">
-        <v>5.036021585604853</v>
+        <v>4.789461580352911</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>10.42281239708319</v>
+        <v>561.9110062426548</v>
       </c>
       <c r="I30" t="n">
-        <v>66.7173481494777</v>
+        <v>3753.07959865759</v>
       </c>
       <c r="J30" t="n">
-        <v>0.05967933756765446</v>
+        <v>2.473221466155956</v>
       </c>
       <c r="K30" t="n">
         <v>1.540690766967645</v>
@@ -1506,25 +1506,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1510373294698574</v>
+        <v>0.1420323022187931</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1207172340937808</v>
+        <v>0.1113905987266071</v>
       </c>
       <c r="F31" t="n">
-        <v>4.981426595017587</v>
+        <v>4.635261295280573</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>10.27659950292629</v>
+        <v>543.6758035124599</v>
       </c>
       <c r="I31" t="n">
-        <v>68.04012980762613</v>
+        <v>3827.832084809528</v>
       </c>
       <c r="J31" t="n">
-        <v>0.05734889566913642</v>
+        <v>2.321379571922138</v>
       </c>
       <c r="K31" t="n">
         <v>1.535645355348145</v>
@@ -1541,25 +1541,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1516738079758333</v>
+        <v>0.1445286244513329</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1224211806646551</v>
+        <v>0.1150296115013788</v>
       </c>
       <c r="F32" t="n">
-        <v>5.184963605572445</v>
+        <v>4.899439337056125</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>10.70956702177532</v>
+        <v>571.823570415762</v>
       </c>
       <c r="I32" t="n">
-        <v>70.60920514029499</v>
+        <v>3956.472792753328</v>
       </c>
       <c r="J32" t="n">
-        <v>0.05780863962212959</v>
+        <v>2.33527995661839</v>
       </c>
       <c r="K32" t="n">
         <v>1.488797037449247</v>
@@ -1576,25 +1576,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1376168293479986</v>
+        <v>0.133788473650519</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1088707236595984</v>
+        <v>0.1049147561055362</v>
       </c>
       <c r="F33" t="n">
-        <v>4.787320788413134</v>
+        <v>4.63357284845945</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>10.07824244714812</v>
+        <v>551.5891918867394</v>
       </c>
       <c r="I33" t="n">
-        <v>73.23408404987129</v>
+        <v>4122.845390460133</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04989681981400761</v>
+        <v>1.947893744790552</v>
       </c>
       <c r="K33" t="n">
         <v>1.400490869902281</v>
@@ -1611,25 +1611,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1331098127817443</v>
+        <v>0.1255772142924206</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1049640274824502</v>
+        <v>0.09718686410710953</v>
       </c>
       <c r="F34" t="n">
-        <v>4.72929823653146</v>
+        <v>4.423235834455944</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>10.05863435175766</v>
+        <v>536.7091168268452</v>
       </c>
       <c r="I34" t="n">
-        <v>75.56643752666432</v>
+        <v>4273.937113918277</v>
       </c>
       <c r="J34" t="n">
-        <v>0.04781987177008215</v>
+        <v>1.801442352029741</v>
       </c>
       <c r="K34" t="n">
         <v>1.340260778898987</v>
@@ -1646,25 +1646,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1364747120997007</v>
+        <v>0.1274925976470202</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1093198288323958</v>
+        <v>0.1000552579503857</v>
       </c>
       <c r="F35" t="n">
-        <v>5.025788943973066</v>
+        <v>4.646682187728946</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>10.7555958940999</v>
+        <v>566.6649815898626</v>
       </c>
       <c r="I35" t="n">
-        <v>78.8101746369135</v>
+        <v>4444.689276460959</v>
       </c>
       <c r="J35" t="n">
-        <v>0.05107270800997977</v>
+        <v>1.938340936394056</v>
       </c>
       <c r="K35" t="n">
         <v>1.275757087929616</v>
@@ -1681,25 +1681,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1223469071727016</v>
+        <v>0.1193543473406576</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09558919092796681</v>
+        <v>0.09250539451567763</v>
       </c>
       <c r="F36" t="n">
-        <v>4.572397212590091</v>
+        <v>4.445400463798043</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>9.869989647396904</v>
+        <v>545.491610869143</v>
       </c>
       <c r="I36" t="n">
-        <v>80.67216307695213</v>
+        <v>4570.35393367128</v>
       </c>
       <c r="J36" t="n">
-        <v>0.04470954274268862</v>
+        <v>1.75438115380514</v>
       </c>
       <c r="K36" t="n">
         <v>1.250863946408975</v>
@@ -1716,25 +1716,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1293040450043632</v>
+        <v>0.1242924158558284</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1033904749152075</v>
+        <v>0.09822969013725191</v>
       </c>
       <c r="F37" t="n">
-        <v>4.989819795554666</v>
+        <v>4.768972255547218</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>10.72023337915683</v>
+        <v>587.5171101404724</v>
       </c>
       <c r="I37" t="n">
-        <v>82.90717725648173</v>
+        <v>4726.894284700011</v>
       </c>
       <c r="J37" t="n">
-        <v>0.04781902177802135</v>
+        <v>1.975410723369358</v>
       </c>
       <c r="K37" t="n">
         <v>1.230859493258122</v>
@@ -1751,25 +1751,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1283135879113764</v>
+        <v>0.1215206596909994</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1031203390070808</v>
+        <v>0.09613108338149068</v>
       </c>
       <c r="F38" t="n">
-        <v>5.093173508459195</v>
+        <v>4.786242125887251</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>10.95546106543624</v>
+        <v>593.8703159143946</v>
       </c>
       <c r="I38" t="n">
-        <v>85.38036574117905</v>
+        <v>4886.990553083545</v>
       </c>
       <c r="J38" t="n">
-        <v>0.04779846018284575</v>
+        <v>1.869721980229309</v>
       </c>
       <c r="K38" t="n">
         <v>1.208248342730408</v>
@@ -1786,25 +1786,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1255833968440966</v>
+        <v>0.1178841133060981</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1010211327105038</v>
+        <v>0.09310557716301104</v>
       </c>
       <c r="F39" t="n">
-        <v>5.112859146903373</v>
+        <v>4.757509185585451</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>10.91683020568811</v>
+        <v>590.3070695118552</v>
       </c>
       <c r="I39" t="n">
-        <v>86.92892914212717</v>
+        <v>5007.520122572094</v>
       </c>
       <c r="J39" t="n">
-        <v>0.04726848964341904</v>
+        <v>1.821226859712368</v>
       </c>
       <c r="K39" t="n">
         <v>1.17660587484867</v>
@@ -1821,25 +1821,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.12039449162844</v>
+        <v>0.111127034670024</v>
       </c>
       <c r="E40" t="n">
-        <v>0.09622950513471584</v>
+        <v>0.08670744771040939</v>
       </c>
       <c r="F40" t="n">
-        <v>4.982187416479928</v>
+        <v>4.550733591596233</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>10.65090174542406</v>
+        <v>568.3186609594753</v>
       </c>
       <c r="I40" t="n">
-        <v>88.46668648508228</v>
+        <v>5114.135031561104</v>
       </c>
       <c r="J40" t="n">
-        <v>0.04531452522257091</v>
+        <v>1.728582689525568</v>
       </c>
       <c r="K40" t="n">
         <v>1.141424383478388</v>
@@ -1856,25 +1856,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.118398379991163</v>
+        <v>0.1099364976014969</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0948261441620496</v>
+        <v>0.08613800823255291</v>
       </c>
       <c r="F41" t="n">
-        <v>5.022789558423351</v>
+        <v>4.619473778237351</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>10.72465217291278</v>
+        <v>579.9362095871379</v>
       </c>
       <c r="I41" t="n">
-        <v>90.58107191764991</v>
+        <v>5275.192699783092</v>
       </c>
       <c r="J41" t="n">
-        <v>0.04524985112674351</v>
+        <v>1.705597600646755</v>
       </c>
       <c r="K41" t="n">
         <v>1.122854526749683</v>
@@ -1891,25 +1891,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.115769414608634</v>
+        <v>0.1040777986195653</v>
       </c>
       <c r="E42" t="n">
-        <v>0.09274257644740047</v>
+        <v>0.08074649129194977</v>
       </c>
       <c r="F42" t="n">
-        <v>5.027586236461065</v>
+        <v>4.46086441527331</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>10.68044323178779</v>
+        <v>559.1823830338781</v>
       </c>
       <c r="I42" t="n">
-        <v>92.25617377347656</v>
+        <v>5372.734535612657</v>
       </c>
       <c r="J42" t="n">
-        <v>0.04397591802240389</v>
+        <v>1.587448531057553</v>
       </c>
       <c r="K42" t="n">
         <v>1.094959332343793</v>
@@ -1926,25 +1926,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1178419295909922</v>
+        <v>0.1036912514808621</v>
       </c>
       <c r="E43" t="n">
-        <v>0.09533789718259911</v>
+        <v>0.08082623238598619</v>
       </c>
       <c r="F43" t="n">
-        <v>5.236480620559457</v>
+        <v>4.53492958176008</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>11.09683399555101</v>
+        <v>567.3813591141443</v>
       </c>
       <c r="I43" t="n">
-        <v>94.16711041703148</v>
+        <v>5471.834422008724</v>
       </c>
       <c r="J43" t="n">
-        <v>0.04506351121852373</v>
+        <v>1.563873193902564</v>
       </c>
       <c r="K43" t="n">
         <v>1.084243217811965</v>
@@ -1961,25 +1961,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1171160633472289</v>
+        <v>0.1024046587768786</v>
       </c>
       <c r="E44" t="n">
-        <v>0.09515377636581668</v>
+        <v>0.08007641645789543</v>
       </c>
       <c r="F44" t="n">
-        <v>5.332598715532223</v>
+        <v>4.586328709350119</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>11.25661508875681</v>
+        <v>572.1030103931042</v>
       </c>
       <c r="I44" t="n">
-        <v>96.1150397907663</v>
+        <v>5586.689289591935</v>
       </c>
       <c r="J44" t="n">
-        <v>0.04506194937414686</v>
+        <v>1.5409572347536</v>
       </c>
       <c r="K44" t="n">
         <v>1.072879655498824</v>
@@ -1996,25 +1996,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1215586271871556</v>
+        <v>0.1045816922803351</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1002372346431545</v>
+        <v>0.0828482382094694</v>
       </c>
       <c r="F45" t="n">
-        <v>5.701251779699398</v>
+        <v>4.812014323141117</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>11.96515610829346</v>
+        <v>592.897699796921</v>
       </c>
       <c r="I45" t="n">
-        <v>98.43115528008981</v>
+        <v>5669.230310479549</v>
       </c>
       <c r="J45" t="n">
-        <v>0.04787049724027319</v>
+        <v>1.622817934112246</v>
       </c>
       <c r="K45" t="n">
         <v>1.053397444760216</v>
@@ -2031,25 +2031,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1182816598929944</v>
+        <v>0.100409779001303</v>
       </c>
       <c r="E46" t="n">
-        <v>0.09728836608092284</v>
+        <v>0.0789909642156198</v>
       </c>
       <c r="F46" t="n">
-        <v>5.63425925211317</v>
+        <v>4.68792414547694</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>11.85996797295131</v>
+        <v>579.1302103491925</v>
       </c>
       <c r="I46" t="n">
-        <v>100.2688665654561</v>
+        <v>5767.667413566132</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04624667216604619</v>
+        <v>1.526695748214419</v>
       </c>
       <c r="K46" t="n">
         <v>1.03745385910538</v>
@@ -2066,25 +2066,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1212951430931017</v>
+        <v>0.102275606002941</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1008601464208482</v>
+        <v>0.08139829451463731</v>
       </c>
       <c r="F47" t="n">
-        <v>5.935657589697368</v>
+        <v>4.898887773947325</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>12.34430503726941</v>
+        <v>599.885325076361</v>
       </c>
       <c r="I47" t="n">
-        <v>101.7708106234261</v>
+        <v>5865.380304459997</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0480334934313023</v>
+        <v>1.548673206619315</v>
       </c>
       <c r="K47" t="n">
         <v>1.021710750376712</v>
@@ -2101,25 +2101,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1228520545628626</v>
+        <v>0.1014695505523736</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1029168739847459</v>
+        <v>0.08104840397401847</v>
       </c>
       <c r="F48" t="n">
-        <v>6.162575457065072</v>
+        <v>4.968846884431239</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>12.6843811612653</v>
+        <v>603.5510813400929</v>
       </c>
       <c r="I48" t="n">
-        <v>103.2492391470326</v>
+        <v>5948.100470087027</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0488472571017978</v>
+        <v>1.512134511877415</v>
       </c>
       <c r="K48" t="n">
         <v>1.010373464728372</v>
@@ -2136,25 +2136,25 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1248915760800551</v>
+        <v>0.1024510271862231</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1053579059032705</v>
+        <v>0.08241645190020119</v>
       </c>
       <c r="F49" t="n">
-        <v>6.393656437820223</v>
+        <v>5.113710958360245</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>13.11341883830757</v>
+        <v>620.6466548662495</v>
       </c>
       <c r="I49" t="n">
-        <v>104.9984254334489</v>
+        <v>6057.983720730425</v>
       </c>
       <c r="J49" t="n">
-        <v>0.04993911090901088</v>
+        <v>1.563048427479076</v>
       </c>
       <c r="K49" t="n">
         <v>1.004489866792857</v>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -488,31 +488,31 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4925408876868616</v>
+        <v>0.4969677356584342</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0149182246262769</v>
+        <v>0.2175053665797866</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9706021149994218</v>
+        <v>1.778299301250736</v>
       </c>
       <c r="G2" t="n">
-        <v>0.525</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>116.788271326476</v>
+        <v>154.5841539569252</v>
       </c>
       <c r="I2" t="n">
-        <v>237.113860485681</v>
+        <v>311.0547081132261</v>
       </c>
       <c r="J2" t="n">
-        <v>5.359957295715329</v>
+        <v>7.140675172357605</v>
       </c>
       <c r="K2" t="n">
-        <v>9.145636738102082</v>
+        <v>6.252383813694603</v>
       </c>
     </row>
     <row r="3">
@@ -523,31 +523,31 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3970233575455657</v>
+        <v>0.3195345128837224</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09553503631834859</v>
+        <v>0.09271268384496323</v>
       </c>
       <c r="F3" t="n">
-        <v>1.316878066551535</v>
+        <v>1.408746742929758</v>
       </c>
       <c r="G3" t="n">
-        <v>0.172</v>
+        <v>0.171</v>
       </c>
       <c r="H3" t="n">
-        <v>154.5841489470177</v>
+        <v>134.4585841535386</v>
       </c>
       <c r="I3" t="n">
-        <v>389.3578199093144</v>
+        <v>420.7951840321789</v>
       </c>
       <c r="J3" t="n">
-        <v>4.710835345943221</v>
+        <v>3.956146071259148</v>
       </c>
       <c r="K3" t="n">
-        <v>7.066033920197936</v>
+        <v>2.950561933156091</v>
       </c>
     </row>
     <row r="4">
@@ -558,31 +558,31 @@
         <v>0.09</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.356658965838565</v>
+        <v>0.2794490256682379</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1268943107809096</v>
+        <v>0.1078892698749611</v>
       </c>
       <c r="F4" t="n">
-        <v>1.552279508565265</v>
+        <v>1.628872834285004</v>
       </c>
       <c r="G4" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="H4" t="n">
-        <v>187.1540776890202</v>
+        <v>162.3815764169076</v>
       </c>
       <c r="I4" t="n">
-        <v>524.7423887101495</v>
+        <v>581.0776259770794</v>
       </c>
       <c r="J4" t="n">
-        <v>5.967576259658116</v>
+        <v>3.627357941606845</v>
       </c>
       <c r="K4" t="n">
-        <v>5.906324511842218</v>
+        <v>3.734885643976462</v>
       </c>
     </row>
     <row r="5">
@@ -593,31 +593,31 @@
         <v>0.11</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2892518523574867</v>
+        <v>0.2399089107781798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1022128661357727</v>
+        <v>0.1041783591314261</v>
       </c>
       <c r="F5" t="n">
-        <v>1.546478935758402</v>
+        <v>1.767538021966906</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.023</v>
       </c>
       <c r="H5" t="n">
-        <v>196.0994682513464</v>
+        <v>168.5189307132035</v>
       </c>
       <c r="I5" t="n">
-        <v>677.9540620157787</v>
+        <v>702.4288100287212</v>
       </c>
       <c r="J5" t="n">
-        <v>5.083107668153946</v>
+        <v>2.969805631203743</v>
       </c>
       <c r="K5" t="n">
-        <v>6.062995790074879</v>
+        <v>2.797713215022664</v>
       </c>
     </row>
     <row r="6">
@@ -628,31 +628,31 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2456088688191881</v>
+        <v>0.2393802083074098</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08844404982318566</v>
+        <v>0.1275243565879113</v>
       </c>
       <c r="F6" t="n">
-        <v>1.562747123613174</v>
+        <v>2.140077650185925</v>
       </c>
       <c r="G6" t="n">
-        <v>0.056</v>
+        <v>0.006</v>
       </c>
       <c r="H6" t="n">
-        <v>203.9583031954551</v>
+        <v>189.3136155813861</v>
       </c>
       <c r="I6" t="n">
-        <v>830.419130123533</v>
+        <v>790.8490719427871</v>
       </c>
       <c r="J6" t="n">
-        <v>5.185312301894066</v>
+        <v>3.240120934636324</v>
       </c>
       <c r="K6" t="n">
-        <v>3.372238329751428</v>
+        <v>2.77486667385637</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +663,31 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1681260770887759</v>
+        <v>0.2305664530048765</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01957716228320017</v>
+        <v>0.1343872596304861</v>
       </c>
       <c r="F7" t="n">
-        <v>1.131789332213051</v>
+        <v>2.397259167139878</v>
       </c>
       <c r="G7" t="n">
-        <v>0.321</v>
+        <v>0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>156.7245605671517</v>
+        <v>216.1055708349847</v>
       </c>
       <c r="I7" t="n">
-        <v>932.1847228041613</v>
+        <v>937.2810659077712</v>
       </c>
       <c r="J7" t="n">
-        <v>3.233123149939415</v>
+        <v>3.232543734994039</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75034946795072</v>
+        <v>3.368374750158203</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +698,31 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1725104632447115</v>
+        <v>0.2078261281880161</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04713326070603141</v>
+        <v>0.1217202725562786</v>
       </c>
       <c r="F8" t="n">
-        <v>1.375931666616109</v>
+        <v>2.413612020497875</v>
       </c>
       <c r="G8" t="n">
-        <v>0.118</v>
+        <v>0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>180.984819443416</v>
+        <v>240.9648803637636</v>
       </c>
       <c r="I8" t="n">
-        <v>1049.123722928524</v>
+        <v>1159.454215235957</v>
       </c>
       <c r="J8" t="n">
-        <v>3.38378656325168</v>
+        <v>3.193258819374302</v>
       </c>
       <c r="K8" t="n">
-        <v>3.535358492741626</v>
+        <v>3.709601366148668</v>
       </c>
     </row>
     <row r="9">
@@ -733,31 +733,31 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1477698430525909</v>
+        <v>0.1628288630300037</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03563429608582658</v>
+        <v>0.08233163832135004</v>
       </c>
       <c r="F9" t="n">
-        <v>1.31777876908549</v>
+        <v>2.022788532391472</v>
       </c>
       <c r="G9" t="n">
-        <v>0.145</v>
+        <v>0.005</v>
       </c>
       <c r="H9" t="n">
-        <v>171.355457598894</v>
+        <v>211.93482021178</v>
       </c>
       <c r="I9" t="n">
-        <v>1159.610473010444</v>
+        <v>1301.580176069447</v>
       </c>
       <c r="J9" t="n">
-        <v>2.587354522628796</v>
+        <v>2.569989382957227</v>
       </c>
       <c r="K9" t="n">
-        <v>3.860154330167111</v>
+        <v>3.465855361209127</v>
       </c>
     </row>
     <row r="10">
@@ -768,31 +768,31 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.160938677631404</v>
+        <v>0.164195816791446</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0610504249684759</v>
+        <v>0.09336495380767029</v>
       </c>
       <c r="F10" t="n">
-        <v>1.611187235144557</v>
+        <v>2.318139436322498</v>
       </c>
       <c r="G10" t="n">
-        <v>0.038</v>
+        <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>199.2998804240868</v>
+        <v>251.424497996859</v>
       </c>
       <c r="I10" t="n">
-        <v>1238.359127571192</v>
+        <v>1531.247889927713</v>
       </c>
       <c r="J10" t="n">
-        <v>2.777751313156684</v>
+        <v>2.850177630114748</v>
       </c>
       <c r="K10" t="n">
-        <v>3.485812317750533</v>
+        <v>3.552211038171513</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +803,31 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.189661878159923</v>
+        <v>0.1590836544229535</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1034556949854466</v>
+        <v>0.09439778168625768</v>
       </c>
       <c r="F11" t="n">
-        <v>2.200095992836829</v>
+        <v>2.459326089183402</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>272.6348351730873</v>
+        <v>260.3924627966227</v>
       </c>
       <c r="I11" t="n">
-        <v>1437.47830517212</v>
+        <v>1636.827263876657</v>
       </c>
       <c r="J11" t="n">
-        <v>3.947597993547647</v>
+        <v>2.556216630594133</v>
       </c>
       <c r="K11" t="n">
-        <v>3.026876285456252</v>
+        <v>3.586775273556275</v>
       </c>
     </row>
     <row r="12">
@@ -838,31 +838,31 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1683130747881656</v>
+        <v>0.1650193377260441</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08834317813318149</v>
+        <v>0.1062178826363289</v>
       </c>
       <c r="F12" t="n">
-        <v>2.104705418269108</v>
+        <v>2.806381873956504</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>259.0013212245683</v>
+        <v>293.1047825156182</v>
       </c>
       <c r="I12" t="n">
-        <v>1538.806902259616</v>
+        <v>1776.184455437668</v>
       </c>
       <c r="J12" t="n">
-        <v>3.44703099723679</v>
+        <v>2.536284311024074</v>
       </c>
       <c r="K12" t="n">
-        <v>2.790293819287251</v>
+        <v>3.773099111617564</v>
       </c>
     </row>
     <row r="13">
@@ -873,31 +873,31 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1556790590251084</v>
+        <v>0.1780787517071065</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08029326072377885</v>
+        <v>0.1247072420776979</v>
       </c>
       <c r="F13" t="n">
-        <v>2.065097969816984</v>
+        <v>3.336588246118897</v>
       </c>
       <c r="G13" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>253.1352608338389</v>
+        <v>349.8628252563662</v>
       </c>
       <c r="I13" t="n">
-        <v>1626.007135571217</v>
+        <v>1964.652278289776</v>
       </c>
       <c r="J13" t="n">
-        <v>3.079566442377794</v>
+        <v>2.586861886661342</v>
       </c>
       <c r="K13" t="n">
-        <v>2.773600083382057</v>
+        <v>3.50243465319796</v>
       </c>
     </row>
     <row r="14">
@@ -908,31 +908,31 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1559241099348409</v>
+        <v>0.1588598897376015</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08673756156884427</v>
+        <v>0.1081887987579389</v>
       </c>
       <c r="F14" t="n">
-        <v>2.253676670066019</v>
+        <v>3.135118795870445</v>
       </c>
       <c r="G14" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>291.4920339690231</v>
+        <v>338.8508263161201</v>
       </c>
       <c r="I14" t="n">
-        <v>1869.448118644606</v>
+        <v>2133.016879690781</v>
       </c>
       <c r="J14" t="n">
-        <v>3.170858811199212</v>
+        <v>2.456543463375225</v>
       </c>
       <c r="K14" t="n">
-        <v>2.870856540458181</v>
+        <v>3.538712340268808</v>
       </c>
     </row>
     <row r="15">
@@ -943,31 +943,31 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1728469102031027</v>
+        <v>0.1628155944138455</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1101837973397015</v>
+        <v>0.1163053496590591</v>
       </c>
       <c r="F15" t="n">
-        <v>2.758351800682005</v>
+        <v>3.500639381113776</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>346.8482057026886</v>
+        <v>370.2647704221824</v>
       </c>
       <c r="I15" t="n">
-        <v>2006.678657403402</v>
+        <v>2274.135789972559</v>
       </c>
       <c r="J15" t="n">
-        <v>3.711231175026501</v>
+        <v>2.587218654794976</v>
       </c>
       <c r="K15" t="n">
-        <v>2.705625660438311</v>
+        <v>3.399426184996742</v>
       </c>
     </row>
     <row r="16">
@@ -978,31 +978,31 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1605148524164015</v>
+        <v>0.1610639176530709</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1005516275890016</v>
+        <v>0.1173693300308351</v>
       </c>
       <c r="F16" t="n">
-        <v>2.676888257401644</v>
+        <v>3.686129711202642</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>337.2639928438506</v>
+        <v>393.3921604325116</v>
       </c>
       <c r="I16" t="n">
-        <v>2101.138852677216</v>
+        <v>2442.459901415486</v>
       </c>
       <c r="J16" t="n">
-        <v>3.297910718256711</v>
+        <v>2.694478910772082</v>
       </c>
       <c r="K16" t="n">
-        <v>2.639838030796089</v>
+        <v>3.448263736336748</v>
       </c>
     </row>
     <row r="17">
@@ -1013,31 +1013,31 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1655664498120034</v>
+        <v>0.1536412405893806</v>
       </c>
       <c r="E17" t="n">
-        <v>0.109937546466137</v>
+        <v>0.1121530661084678</v>
       </c>
       <c r="F17" t="n">
-        <v>2.976266650137117</v>
+        <v>3.703253818990414</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>371.028394383361</v>
+        <v>389.8468619509503</v>
       </c>
       <c r="I17" t="n">
-        <v>2240.963642118645</v>
+        <v>2537.384236520515</v>
       </c>
       <c r="J17" t="n">
-        <v>3.546265171548783</v>
+        <v>2.497969399207014</v>
       </c>
       <c r="K17" t="n">
-        <v>2.731893165862686</v>
+        <v>3.075077501588781</v>
       </c>
     </row>
     <row r="18">
@@ -1048,31 +1048,31 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1594273508962541</v>
+        <v>0.1354542565893837</v>
       </c>
       <c r="E18" t="n">
-        <v>0.10689156032727</v>
+        <v>0.09542899069074406</v>
       </c>
       <c r="F18" t="n">
-        <v>3.034642653505175</v>
+        <v>3.384218781516888</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>389.0544489102685</v>
+        <v>390.2443870676665</v>
       </c>
       <c r="I18" t="n">
-        <v>2440.324365443682</v>
+        <v>2881.004974621463</v>
       </c>
       <c r="J18" t="n">
-        <v>3.302255441161214</v>
+        <v>2.380537621773903</v>
       </c>
       <c r="K18" t="n">
-        <v>2.556364796081964</v>
+        <v>2.991901472158265</v>
       </c>
     </row>
     <row r="19">
@@ -1083,31 +1083,31 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1576762124348407</v>
+        <v>0.1363408333660704</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1075378917464382</v>
+        <v>0.09846104535581035</v>
       </c>
       <c r="F19" t="n">
-        <v>3.144824363280146</v>
+        <v>3.599302966773239</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>395.6873803563738</v>
+        <v>419.7346581619117</v>
       </c>
       <c r="I19" t="n">
-        <v>2509.493183823722</v>
+        <v>3078.568964258409</v>
       </c>
       <c r="J19" t="n">
-        <v>3.16157645007891</v>
+        <v>2.270040433622865</v>
       </c>
       <c r="K19" t="n">
-        <v>2.330223407508293</v>
+        <v>2.866226220104054</v>
       </c>
     </row>
     <row r="20">
@@ -1118,31 +1118,31 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1510311715867109</v>
+        <v>0.1324035295186386</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1033362935859645</v>
+        <v>0.0965524356970946</v>
       </c>
       <c r="F20" t="n">
-        <v>3.166611970038938</v>
+        <v>3.693151739740612</v>
       </c>
       <c r="G20" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>398.3174512257812</v>
+        <v>430.7487666967266</v>
       </c>
       <c r="I20" t="n">
-        <v>2637.31948207193</v>
+        <v>3253.302750030464</v>
       </c>
       <c r="J20" t="n">
-        <v>2.846522369821444</v>
+        <v>2.191967796086555</v>
       </c>
       <c r="K20" t="n">
-        <v>2.232683500945971</v>
+        <v>2.648759281927748</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1530262536691974</v>
+        <v>0.1290534761558634</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1079744586516016</v>
+        <v>0.09476424293365338</v>
       </c>
       <c r="F21" t="n">
-        <v>3.396673841950801</v>
+        <v>3.763673434151682</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>422.3620976787218</v>
+        <v>446.6388169857011</v>
       </c>
       <c r="I21" t="n">
-        <v>2760.062979727373</v>
+        <v>3460.881723528905</v>
       </c>
       <c r="J21" t="n">
-        <v>2.840168227951631</v>
+        <v>2.136207383566929</v>
       </c>
       <c r="K21" t="n">
-        <v>2.107938184256481</v>
+        <v>2.691300192575502</v>
       </c>
     </row>
     <row r="22">
@@ -1188,31 +1188,31 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1532354754980822</v>
+        <v>0.1255133369224385</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1100332038398212</v>
+        <v>0.092637898460876</v>
       </c>
       <c r="F22" t="n">
-        <v>3.546930974144287</v>
+        <v>3.817845260655218</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>440.0112574103838</v>
+        <v>452.873106472872</v>
       </c>
       <c r="I22" t="n">
-        <v>2871.471217615602</v>
+        <v>3608.167208180648</v>
       </c>
       <c r="J22" t="n">
-        <v>2.833777676689714</v>
+        <v>2.02918795095515</v>
       </c>
       <c r="K22" t="n">
-        <v>2.028603484267691</v>
+        <v>2.676320284562453</v>
       </c>
     </row>
     <row r="23">
@@ -1223,31 +1223,31 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1453323851435263</v>
+        <v>0.1193646325841079</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1038436659757364</v>
+        <v>0.08768710138209734</v>
       </c>
       <c r="F23" t="n">
-        <v>3.502937378128461</v>
+        <v>3.768116644662387</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>428.7638148078412</v>
+        <v>455.2628568104861</v>
       </c>
       <c r="I23" t="n">
-        <v>2950.228982923563</v>
+        <v>3814.051507172313</v>
       </c>
       <c r="J23" t="n">
-        <v>2.740696936599851</v>
+        <v>1.93276784838527</v>
       </c>
       <c r="K23" t="n">
-        <v>1.942216420625014</v>
+        <v>2.630663019490783</v>
       </c>
     </row>
     <row r="24">
@@ -1258,31 +1258,31 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.162248237343661</v>
+        <v>0.1132105053409128</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1234634335169786</v>
+        <v>0.08263155724922011</v>
       </c>
       <c r="F24" t="n">
-        <v>4.183294005268137</v>
+        <v>3.702236748021705</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>508.257297814339</v>
+        <v>446.7653072212604</v>
       </c>
       <c r="I24" t="n">
-        <v>3132.590566995127</v>
+        <v>3946.323760996457</v>
       </c>
       <c r="J24" t="n">
-        <v>2.978442996777887</v>
+        <v>1.769994820502533</v>
       </c>
       <c r="K24" t="n">
-        <v>1.868953081065527</v>
+        <v>2.527794786391687</v>
       </c>
     </row>
     <row r="25">
@@ -1293,31 +1293,31 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1569135331589881</v>
+        <v>0.1137619981471828</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1192757444607286</v>
+        <v>0.0846094322967611</v>
       </c>
       <c r="F25" t="n">
-        <v>4.169042299933113</v>
+        <v>3.902297956580639</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>509.9235183857994</v>
+        <v>471.4898623310264</v>
       </c>
       <c r="I25" t="n">
-        <v>3249.710258382456</v>
+        <v>4144.528665196465</v>
       </c>
       <c r="J25" t="n">
-        <v>2.861502134773557</v>
+        <v>1.724641773577072</v>
       </c>
       <c r="K25" t="n">
-        <v>1.840631994946188</v>
+        <v>2.477689307763795</v>
       </c>
     </row>
     <row r="26">
@@ -1328,31 +1328,31 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1616065009425485</v>
+        <v>0.1133561150106158</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1257777189315462</v>
+        <v>0.08529776421981261</v>
       </c>
       <c r="F26" t="n">
-        <v>4.51052176132928</v>
+        <v>4.040013465359149</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>542.5791391529224</v>
+        <v>492.3676457357433</v>
       </c>
       <c r="I26" t="n">
-        <v>3357.409114041832</v>
+        <v>4343.547286263587</v>
       </c>
       <c r="J26" t="n">
-        <v>2.831863585982722</v>
+        <v>1.742372113925561</v>
       </c>
       <c r="K26" t="n">
-        <v>1.767252564395192</v>
+        <v>2.434162875981269</v>
       </c>
     </row>
     <row r="27">
@@ -1363,31 +1363,31 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1611367856924726</v>
+        <v>0.1071268776304835</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1267571457618363</v>
+        <v>0.07990513609482741</v>
       </c>
       <c r="F27" t="n">
-        <v>4.6869829357602</v>
+        <v>3.935342545595951</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>558.3611995045231</v>
+        <v>479.4593944067186</v>
       </c>
       <c r="I27" t="n">
-        <v>3465.138001264018</v>
+        <v>4475.621851507095</v>
       </c>
       <c r="J27" t="n">
-        <v>2.807130603273303</v>
+        <v>1.684404504554075</v>
       </c>
       <c r="K27" t="n">
-        <v>1.723871423516526</v>
+        <v>2.354635637465393</v>
       </c>
     </row>
     <row r="28">
@@ -1398,31 +1398,31 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1585398479594011</v>
+        <v>0.1057154973688664</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1251485720847741</v>
+        <v>0.07941301199736261</v>
       </c>
       <c r="F28" t="n">
-        <v>4.747942203666165</v>
+        <v>4.019220840757446</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>561.529282412726</v>
+        <v>486.9198715499572</v>
       </c>
       <c r="I28" t="n">
-        <v>3541.881045303655</v>
+        <v>4605.945993433474</v>
       </c>
       <c r="J28" t="n">
-        <v>2.732309827059296</v>
+        <v>1.61835153631411</v>
       </c>
       <c r="K28" t="n">
-        <v>1.656345173559502</v>
+        <v>2.232141800456855</v>
       </c>
     </row>
     <row r="29">
@@ -1433,31 +1433,31 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1573926571234671</v>
+        <v>0.1038606038689584</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1252320715174927</v>
+        <v>0.0784020982970538</v>
       </c>
       <c r="F29" t="n">
-        <v>4.893961168860929</v>
+        <v>4.079603320611894</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>579.4287909260013</v>
+        <v>491.2493046432697</v>
       </c>
       <c r="I29" t="n">
-        <v>3681.422002244149</v>
+        <v>4729.890702956843</v>
       </c>
       <c r="J29" t="n">
-        <v>2.600914928441721</v>
+        <v>1.59091164153798</v>
       </c>
       <c r="K29" t="n">
-        <v>1.638857066983883</v>
+        <v>2.14811905187862</v>
       </c>
     </row>
     <row r="30">
@@ -1468,31 +1468,31 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1497199810106986</v>
+        <v>0.09846900095041315</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1184596861949154</v>
+        <v>0.07383700644086155</v>
       </c>
       <c r="F30" t="n">
-        <v>4.789461580352911</v>
+        <v>3.997605671446127</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>561.9110062426548</v>
+        <v>484.5600901467915</v>
       </c>
       <c r="I30" t="n">
-        <v>3753.07959865759</v>
+        <v>4920.940453034609</v>
       </c>
       <c r="J30" t="n">
-        <v>2.473221466155956</v>
+        <v>1.48210142370289</v>
       </c>
       <c r="K30" t="n">
-        <v>1.540690766967645</v>
+        <v>2.045973748201694</v>
       </c>
     </row>
     <row r="31">
@@ -1503,31 +1503,31 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1420323022187931</v>
+        <v>0.09783094100908708</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1113905987266071</v>
+        <v>0.07396403468657609</v>
       </c>
       <c r="F31" t="n">
-        <v>4.635261295280573</v>
+        <v>4.099020614029659</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>543.6758035124599</v>
+        <v>506.2134613628309</v>
       </c>
       <c r="I31" t="n">
-        <v>3827.832084809528</v>
+        <v>5174.369745823165</v>
       </c>
       <c r="J31" t="n">
-        <v>2.321379571922138</v>
+        <v>1.433260408635041</v>
       </c>
       <c r="K31" t="n">
-        <v>1.535645355348145</v>
+        <v>1.92595060679974</v>
       </c>
     </row>
     <row r="32">
@@ -1538,31 +1538,31 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1445286244513329</v>
+        <v>0.09435206250613606</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1150296115013788</v>
+        <v>0.07113032051911394</v>
       </c>
       <c r="F32" t="n">
-        <v>4.899439337056125</v>
+        <v>4.06309150101083</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>571.823570415762</v>
+        <v>503.7762251150949</v>
       </c>
       <c r="I32" t="n">
-        <v>3956.472792753328</v>
+        <v>5339.3239292711</v>
       </c>
       <c r="J32" t="n">
-        <v>2.33527995661839</v>
+        <v>1.395231700390298</v>
       </c>
       <c r="K32" t="n">
-        <v>1.488797037449247</v>
+        <v>1.809089736002396</v>
       </c>
     </row>
     <row r="33">
@@ -1573,31 +1573,31 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.133788473650519</v>
+        <v>0.09356794357990479</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1049147561055362</v>
+        <v>0.0710198824749273</v>
       </c>
       <c r="F33" t="n">
-        <v>4.63357284845945</v>
+        <v>4.149711283124455</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>551.5891918867394</v>
+        <v>507.4294710666676</v>
       </c>
       <c r="I33" t="n">
-        <v>4122.845390460133</v>
+        <v>5423.112357207412</v>
       </c>
       <c r="J33" t="n">
-        <v>1.947893744790552</v>
+        <v>1.332255235244835</v>
       </c>
       <c r="K33" t="n">
-        <v>1.400490869902281</v>
+        <v>1.670549334079176</v>
       </c>
     </row>
     <row r="34">
@@ -1608,31 +1608,31 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1255772142924206</v>
+        <v>0.09728936868310104</v>
       </c>
       <c r="E34" t="n">
-        <v>0.09718686410710953</v>
+        <v>0.07548476406191973</v>
       </c>
       <c r="F34" t="n">
-        <v>4.423235834455944</v>
+        <v>4.461872635314538</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>536.7091168268452</v>
+        <v>551.1964034672167</v>
       </c>
       <c r="I34" t="n">
-        <v>4273.937113918277</v>
+        <v>5665.535822959435</v>
       </c>
       <c r="J34" t="n">
-        <v>1.801442352029741</v>
+        <v>1.361412122518245</v>
       </c>
       <c r="K34" t="n">
-        <v>1.340260778898987</v>
+        <v>1.578211940789238</v>
       </c>
     </row>
     <row r="35">
@@ -1643,31 +1643,31 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1274925976470202</v>
+        <v>0.0988977614300664</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1000552579503857</v>
+        <v>0.07784397080927341</v>
       </c>
       <c r="F35" t="n">
-        <v>4.646682187728946</v>
+        <v>4.697385055800565</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>566.6649815898626</v>
+        <v>582.4234953992807</v>
       </c>
       <c r="I35" t="n">
-        <v>4444.689276460959</v>
+        <v>5889.147408165856</v>
       </c>
       <c r="J35" t="n">
-        <v>1.938340936394056</v>
+        <v>1.344021149410771</v>
       </c>
       <c r="K35" t="n">
-        <v>1.275757087929616</v>
+        <v>1.516646728390403</v>
       </c>
     </row>
     <row r="36">
@@ -1678,31 +1678,31 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1193543473406576</v>
+        <v>0.1023131228006478</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09250539451567763</v>
+        <v>0.08191114831884427</v>
       </c>
       <c r="F36" t="n">
-        <v>4.445400463798043</v>
+        <v>5.01486377663598</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>545.491610869143</v>
+        <v>625.7425036300251</v>
       </c>
       <c r="I36" t="n">
-        <v>4570.35393367128</v>
+        <v>6115.955475714043</v>
       </c>
       <c r="J36" t="n">
-        <v>1.75438115380514</v>
+        <v>1.380980349769698</v>
       </c>
       <c r="K36" t="n">
-        <v>1.250863946408975</v>
+        <v>1.472902712595847</v>
       </c>
     </row>
     <row r="37">
@@ -1713,31 +1713,31 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1242924158558284</v>
+        <v>0.1086500417539542</v>
       </c>
       <c r="E37" t="n">
-        <v>0.09822969013725191</v>
+        <v>0.08892990993435146</v>
       </c>
       <c r="F37" t="n">
-        <v>4.768972255547218</v>
+        <v>5.509600176503423</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>587.5171101404724</v>
+        <v>685.9187549687533</v>
       </c>
       <c r="I37" t="n">
-        <v>4726.894284700011</v>
+        <v>6313.101623302319</v>
       </c>
       <c r="J37" t="n">
-        <v>1.975410723369358</v>
+        <v>1.36542377528292</v>
       </c>
       <c r="K37" t="n">
-        <v>1.230859493258122</v>
+        <v>1.388299971132925</v>
       </c>
     </row>
     <row r="38">
@@ -1748,31 +1748,31 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1215206596909994</v>
+        <v>0.1119486744964674</v>
       </c>
       <c r="E38" t="n">
-        <v>0.09613108338149068</v>
+        <v>0.09280963730889125</v>
       </c>
       <c r="F38" t="n">
-        <v>4.786242125887251</v>
+        <v>5.849232299372796</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>593.8703159143946</v>
+        <v>724.8582653675917</v>
       </c>
       <c r="I38" t="n">
-        <v>4886.990553083545</v>
+        <v>6474.916015110702</v>
       </c>
       <c r="J38" t="n">
-        <v>1.869721980229309</v>
+        <v>1.380151091840623</v>
       </c>
       <c r="K38" t="n">
-        <v>1.208248342730408</v>
+        <v>1.329951878481112</v>
       </c>
     </row>
     <row r="39">
@@ -1783,31 +1783,31 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1178841133060981</v>
+        <v>0.1150218744362547</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09310557716301104</v>
+        <v>0.09642989700844495</v>
       </c>
       <c r="F39" t="n">
-        <v>4.757509185585451</v>
+        <v>6.186640172239324</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>590.3070695118552</v>
+        <v>765.4090319642503</v>
       </c>
       <c r="I39" t="n">
-        <v>5007.520122572094</v>
+        <v>6654.464950390295</v>
       </c>
       <c r="J39" t="n">
-        <v>1.821226859712368</v>
+        <v>1.413399556577735</v>
       </c>
       <c r="K39" t="n">
-        <v>1.17660587484867</v>
+        <v>1.295130211016425</v>
       </c>
     </row>
     <row r="40">
@@ -1818,31 +1818,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.111127034670024</v>
+        <v>0.1189335366623673</v>
       </c>
       <c r="E40" t="n">
-        <v>0.08670744771040939</v>
+        <v>0.100952588430987</v>
       </c>
       <c r="F40" t="n">
-        <v>4.550733591596233</v>
+        <v>6.614419614133871</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>568.3186609594753</v>
+        <v>815.9897496778354</v>
       </c>
       <c r="I40" t="n">
-        <v>5114.135031561104</v>
+        <v>6860.888632230754</v>
       </c>
       <c r="J40" t="n">
-        <v>1.728582689525568</v>
+        <v>1.409918721216019</v>
       </c>
       <c r="K40" t="n">
-        <v>1.141424383478388</v>
+        <v>1.215527685321818</v>
       </c>
     </row>
     <row r="41">
@@ -1853,31 +1853,31 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1099364976014969</v>
+        <v>0.1219813121587861</v>
       </c>
       <c r="E41" t="n">
-        <v>0.08613800823255291</v>
+        <v>0.1044909000503953</v>
       </c>
       <c r="F41" t="n">
-        <v>4.619473778237351</v>
+        <v>6.974181706117017</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>579.9362095871379</v>
+        <v>864.3529171622284</v>
       </c>
       <c r="I41" t="n">
-        <v>5275.192699783092</v>
+        <v>7085.945394955902</v>
       </c>
       <c r="J41" t="n">
-        <v>1.705597600646755</v>
+        <v>1.444075554133148</v>
       </c>
       <c r="K41" t="n">
-        <v>1.122854526749683</v>
+        <v>1.177216619973364</v>
       </c>
     </row>
     <row r="42">
@@ -1888,31 +1888,31 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1040777986195653</v>
+        <v>0.1177345381334197</v>
       </c>
       <c r="E42" t="n">
-        <v>0.08074649129194977</v>
+        <v>0.1005698404317353</v>
       </c>
       <c r="F42" t="n">
-        <v>4.46086441527331</v>
+        <v>6.859109328902773</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>559.1823830338781</v>
+        <v>851.0754563107732</v>
       </c>
       <c r="I42" t="n">
-        <v>5372.734535612657</v>
+        <v>7228.76625503311</v>
       </c>
       <c r="J42" t="n">
-        <v>1.587448531057553</v>
+        <v>1.362269863154329</v>
       </c>
       <c r="K42" t="n">
-        <v>1.094959332343793</v>
+        <v>1.142697730068748</v>
       </c>
     </row>
     <row r="43">
@@ -1923,31 +1923,31 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1036912514808621</v>
+        <v>0.1221396330711687</v>
       </c>
       <c r="E43" t="n">
-        <v>0.08082623238598619</v>
+        <v>0.105450272483168</v>
       </c>
       <c r="F43" t="n">
-        <v>4.53492958176008</v>
+        <v>7.318412974969531</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>567.3813591141443</v>
+        <v>904.5968608548633</v>
       </c>
       <c r="I43" t="n">
-        <v>5471.834422008724</v>
+        <v>7406.251665483311</v>
       </c>
       <c r="J43" t="n">
-        <v>1.563873193902564</v>
+        <v>1.422612379956793</v>
       </c>
       <c r="K43" t="n">
-        <v>1.084243217811965</v>
+        <v>1.09925429260382</v>
       </c>
     </row>
     <row r="44">
@@ -1958,31 +1958,31 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1024046587768786</v>
+        <v>0.1220609605161287</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08007641645789543</v>
+        <v>0.1057423910089936</v>
       </c>
       <c r="F44" t="n">
-        <v>4.586328709350119</v>
+        <v>7.479881153967487</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>572.1030103931042</v>
+        <v>918.7292621490581</v>
       </c>
       <c r="I44" t="n">
-        <v>5586.689289591935</v>
+        <v>7526.806755118563</v>
       </c>
       <c r="J44" t="n">
-        <v>1.5409572347536</v>
+        <v>1.452589736761587</v>
       </c>
       <c r="K44" t="n">
-        <v>1.072879655498824</v>
+        <v>1.08294003160162</v>
       </c>
     </row>
     <row r="45">
@@ -1993,31 +1993,31 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1045816922803351</v>
+        <v>0.1224822807889025</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0828482382094694</v>
+        <v>0.1065852206582666</v>
       </c>
       <c r="F45" t="n">
-        <v>4.812014323141117</v>
+        <v>7.704712681614773</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>592.897699796921</v>
+        <v>945.9318763873773</v>
       </c>
       <c r="I45" t="n">
-        <v>5669.230310479549</v>
+        <v>7723.009975766909</v>
       </c>
       <c r="J45" t="n">
-        <v>1.622817934112246</v>
+        <v>1.48193769526809</v>
       </c>
       <c r="K45" t="n">
-        <v>1.053397444760216</v>
+        <v>1.057437176339367</v>
       </c>
     </row>
     <row r="46">
@@ -2028,31 +2028,31 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.100409779001303</v>
+        <v>0.1206446608299852</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0789909642156198</v>
+        <v>0.1050532541071126</v>
       </c>
       <c r="F46" t="n">
-        <v>4.68792414547694</v>
+        <v>7.737894532184799</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>579.1302103491925</v>
+        <v>944.9599637287699</v>
       </c>
       <c r="I46" t="n">
-        <v>5767.667413566132</v>
+        <v>7832.588340236835</v>
       </c>
       <c r="J46" t="n">
-        <v>1.526695748214419</v>
+        <v>1.554015781451876</v>
       </c>
       <c r="K46" t="n">
-        <v>1.03745385910538</v>
+        <v>1.040965842293198</v>
       </c>
     </row>
     <row r="47">
@@ -2063,31 +2063,31 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.102275606002941</v>
+        <v>0.1195707540536134</v>
       </c>
       <c r="E47" t="n">
-        <v>0.08139829451463731</v>
+        <v>0.1042855240892665</v>
       </c>
       <c r="F47" t="n">
-        <v>4.898887773947325</v>
+        <v>7.822633636033864</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>599.885325076361</v>
+        <v>955.2299584915445</v>
       </c>
       <c r="I47" t="n">
-        <v>5865.380304459997</v>
+        <v>7988.826080859505</v>
       </c>
       <c r="J47" t="n">
-        <v>1.548673206619315</v>
+        <v>1.61212674302741</v>
       </c>
       <c r="K47" t="n">
-        <v>1.021710750376712</v>
+        <v>1.031291035513255</v>
       </c>
     </row>
     <row r="48">
@@ -2098,31 +2098,31 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1014695505523736</v>
+        <v>0.1239856131712584</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08104840397401847</v>
+        <v>0.1090874093136268</v>
       </c>
       <c r="F48" t="n">
-        <v>4.968846884431239</v>
+        <v>8.32218530207226</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>603.5510813400929</v>
+        <v>1010.664088048337</v>
       </c>
       <c r="I48" t="n">
-        <v>5948.100470087027</v>
+        <v>8151.462594715167</v>
       </c>
       <c r="J48" t="n">
-        <v>1.512134511877415</v>
+        <v>1.738570708180128</v>
       </c>
       <c r="K48" t="n">
-        <v>1.010373464728372</v>
+        <v>1.019519235432884</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1024510271862231</v>
+        <v>0.1291762543223363</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08241645190020119</v>
+        <v>0.1146625252277086</v>
       </c>
       <c r="F49" t="n">
-        <v>5.113710958360245</v>
+        <v>8.900280105831035</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>620.6466548662495</v>
+        <v>1070.792026399236</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.983720730425</v>
+        <v>8289.387488564778</v>
       </c>
       <c r="J49" t="n">
-        <v>1.563048427479076</v>
+        <v>1.905197556405317</v>
       </c>
       <c r="K49" t="n">
-        <v>1.004489866792857</v>
+        <v>1.004144664826493</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4969677356584342</v>
+        <v>0.4988483757108156</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2175053665797866</v>
+        <v>0.2204308066612688</v>
       </c>
       <c r="F2" t="n">
-        <v>1.778299301250736</v>
+        <v>1.791727359066344</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="H2" t="n">
-        <v>154.5841539569252</v>
+        <v>167.0826153028156</v>
       </c>
       <c r="I2" t="n">
-        <v>311.0547081132261</v>
+        <v>334.9366730216117</v>
       </c>
       <c r="J2" t="n">
-        <v>7.140675172357605</v>
+        <v>6.997358742241607</v>
       </c>
       <c r="K2" t="n">
-        <v>6.252383813694603</v>
+        <v>23.74251664848533</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3195345128837224</v>
+        <v>0.3697652713545539</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09271268384496323</v>
+        <v>0.1596870284727385</v>
       </c>
       <c r="F3" t="n">
-        <v>1.408746742929758</v>
+        <v>1.760131207697573</v>
       </c>
       <c r="G3" t="n">
-        <v>0.171</v>
+        <v>0.018</v>
       </c>
       <c r="H3" t="n">
-        <v>134.4585841535386</v>
+        <v>161.8491839603604</v>
       </c>
       <c r="I3" t="n">
-        <v>420.7951840321789</v>
+        <v>437.7079095812906</v>
       </c>
       <c r="J3" t="n">
-        <v>3.956146071259148</v>
+        <v>5.037837005112586</v>
       </c>
       <c r="K3" t="n">
-        <v>2.950561933156091</v>
+        <v>7.4190386708739</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2794490256682379</v>
+        <v>0.2535108775245838</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1078892698749611</v>
+        <v>0.07577537217329422</v>
       </c>
       <c r="F4" t="n">
-        <v>1.628872834285004</v>
+        <v>1.426337844110135</v>
       </c>
       <c r="G4" t="n">
-        <v>0.058</v>
+        <v>0.08</v>
       </c>
       <c r="H4" t="n">
-        <v>162.3815764169076</v>
+        <v>125.7181250409903</v>
       </c>
       <c r="I4" t="n">
-        <v>581.0776259770794</v>
+        <v>495.908208233783</v>
       </c>
       <c r="J4" t="n">
-        <v>3.627357941606845</v>
+        <v>2.696084412951411</v>
       </c>
       <c r="K4" t="n">
-        <v>3.734885643976462</v>
+        <v>5.313124239949635</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2399089107781798</v>
+        <v>0.1811835186616268</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1041783591314261</v>
+        <v>0.03496628985120309</v>
       </c>
       <c r="F5" t="n">
-        <v>1.767538021966906</v>
+        <v>1.239139328078349</v>
       </c>
       <c r="G5" t="n">
-        <v>0.023</v>
+        <v>0.175</v>
       </c>
       <c r="H5" t="n">
-        <v>168.5189307132035</v>
+        <v>120.5440663341085</v>
       </c>
       <c r="I5" t="n">
-        <v>702.4288100287212</v>
+        <v>665.3147439929851</v>
       </c>
       <c r="J5" t="n">
-        <v>2.969805631203743</v>
+        <v>1.911429019135975</v>
       </c>
       <c r="K5" t="n">
-        <v>2.797713215022664</v>
+        <v>6.183240909327947</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2393802083074098</v>
+        <v>0.1752220760971634</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1275243565879113</v>
+        <v>0.05393120493498171</v>
       </c>
       <c r="F6" t="n">
-        <v>2.140077650185925</v>
+        <v>1.444643561532908</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006</v>
+        <v>0.051</v>
       </c>
       <c r="H6" t="n">
-        <v>189.3136155813861</v>
+        <v>141.094153038281</v>
       </c>
       <c r="I6" t="n">
-        <v>790.8490719427871</v>
+        <v>805.2304605730275</v>
       </c>
       <c r="J6" t="n">
-        <v>3.240120934636324</v>
+        <v>1.80572554336702</v>
       </c>
       <c r="K6" t="n">
-        <v>2.77486667385637</v>
+        <v>5.847355147996512</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2305664530048765</v>
+        <v>0.1688900263111286</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1343872596304861</v>
+        <v>0.06500127960001967</v>
       </c>
       <c r="F7" t="n">
-        <v>2.397259167139878</v>
+        <v>1.625681622483844</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002</v>
+        <v>0.021</v>
       </c>
       <c r="H7" t="n">
-        <v>216.1055708349847</v>
+        <v>165.3218530757384</v>
       </c>
       <c r="I7" t="n">
-        <v>937.2810659077712</v>
+        <v>978.8728007607924</v>
       </c>
       <c r="J7" t="n">
-        <v>3.232543734994039</v>
+        <v>1.9768514782428</v>
       </c>
       <c r="K7" t="n">
-        <v>3.368374750158203</v>
+        <v>2.981100598213823</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2078261281880161</v>
+        <v>0.1746985544104379</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1217202725562786</v>
+        <v>0.08499187554200727</v>
       </c>
       <c r="F8" t="n">
-        <v>2.413612020497875</v>
+        <v>1.947442003361439</v>
       </c>
       <c r="G8" t="n">
         <v>0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>240.9648803637636</v>
+        <v>205.9641190159184</v>
       </c>
       <c r="I8" t="n">
-        <v>1159.454215235957</v>
+        <v>1178.96865094845</v>
       </c>
       <c r="J8" t="n">
-        <v>3.193258819374302</v>
+        <v>2.1345587138727</v>
       </c>
       <c r="K8" t="n">
-        <v>3.709601366148668</v>
+        <v>3.086226305846678</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1628288630300037</v>
+        <v>0.1378692782092561</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08233163832135004</v>
+        <v>0.05497209342168452</v>
       </c>
       <c r="F9" t="n">
-        <v>2.022788532391472</v>
+        <v>1.663135829793901</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="H9" t="n">
-        <v>211.93482021178</v>
+        <v>179.7066285435228</v>
       </c>
       <c r="I9" t="n">
-        <v>1301.580176069447</v>
+        <v>1303.456657477865</v>
       </c>
       <c r="J9" t="n">
-        <v>2.569989382957227</v>
+        <v>1.462510029048727</v>
       </c>
       <c r="K9" t="n">
-        <v>3.465855361209127</v>
+        <v>2.468870550243101</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.164195816791446</v>
+        <v>0.1388880330146346</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09336495380767029</v>
+        <v>0.06591244259214601</v>
       </c>
       <c r="F10" t="n">
-        <v>2.318139436322498</v>
+        <v>1.903212186575664</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H10" t="n">
-        <v>251.424497996859</v>
+        <v>205.8547624819415</v>
       </c>
       <c r="I10" t="n">
-        <v>1531.247889927713</v>
+        <v>1482.163423397685</v>
       </c>
       <c r="J10" t="n">
-        <v>2.850177630114748</v>
+        <v>1.414420822971376</v>
       </c>
       <c r="K10" t="n">
-        <v>3.552211038171513</v>
+        <v>2.554694706942387</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1590836544229535</v>
+        <v>0.1481606611145674</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09439778168625768</v>
+        <v>0.08263455812338028</v>
       </c>
       <c r="F11" t="n">
-        <v>2.459326089183402</v>
+        <v>2.261093737475799</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H11" t="n">
-        <v>260.3924627966227</v>
+        <v>250.7090172446334</v>
       </c>
       <c r="I11" t="n">
-        <v>1636.827263876657</v>
+        <v>1692.142943738413</v>
       </c>
       <c r="J11" t="n">
-        <v>2.556216630594133</v>
+        <v>1.680630982589203</v>
       </c>
       <c r="K11" t="n">
-        <v>3.586775273556275</v>
+        <v>2.002294262028931</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1650193377260441</v>
+        <v>0.1481938767261186</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1062178826363289</v>
+        <v>0.08820753001669046</v>
       </c>
       <c r="F12" t="n">
-        <v>2.806381873956504</v>
+        <v>2.470460110597574</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>293.1047825156182</v>
+        <v>274.726168340595</v>
       </c>
       <c r="I12" t="n">
-        <v>1776.184455437668</v>
+        <v>1853.829418662989</v>
       </c>
       <c r="J12" t="n">
-        <v>2.536284311024074</v>
+        <v>1.86531727914471</v>
       </c>
       <c r="K12" t="n">
-        <v>3.773099111617564</v>
+        <v>2.21569091045874</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1780787517071065</v>
+        <v>0.1544444896642789</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1247072420776979</v>
+        <v>0.09953828769442696</v>
       </c>
       <c r="F13" t="n">
-        <v>3.336588246118897</v>
+        <v>2.812878766392938</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>349.8628252563662</v>
+        <v>306.4460165974878</v>
       </c>
       <c r="I13" t="n">
-        <v>1964.652278289776</v>
+        <v>1984.182260329389</v>
       </c>
       <c r="J13" t="n">
-        <v>2.586861886661342</v>
+        <v>1.923154422312094</v>
       </c>
       <c r="K13" t="n">
-        <v>3.50243465319796</v>
+        <v>2.337386646785406</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1588598897376015</v>
+        <v>0.1172981655368419</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1081887987579389</v>
+        <v>0.0641233562318323</v>
       </c>
       <c r="F14" t="n">
-        <v>3.135118795870445</v>
+        <v>2.2058972485265</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>338.8508263161201</v>
+        <v>251.9423288066885</v>
       </c>
       <c r="I14" t="n">
-        <v>2133.016879690781</v>
+        <v>2147.879531223842</v>
       </c>
       <c r="J14" t="n">
-        <v>2.456543463375225</v>
+        <v>1.226950452763834</v>
       </c>
       <c r="K14" t="n">
-        <v>3.538712340268808</v>
+        <v>2.215116950402255</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1628155944138455</v>
+        <v>0.1341623841392923</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1163053496590591</v>
+        <v>0.08606029436925289</v>
       </c>
       <c r="F15" t="n">
-        <v>3.500639381113776</v>
+        <v>2.789117578481094</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>370.2647704221824</v>
+        <v>315.1753012866978</v>
       </c>
       <c r="I15" t="n">
-        <v>2274.135789972559</v>
+        <v>2349.207665834794</v>
       </c>
       <c r="J15" t="n">
-        <v>2.587218654794976</v>
+        <v>1.744431095710618</v>
       </c>
       <c r="K15" t="n">
-        <v>3.399426184996742</v>
+        <v>2.302421503937218</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1610639176530709</v>
+        <v>0.1294446720046985</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1173693300308351</v>
+        <v>0.0841032486716099</v>
       </c>
       <c r="F16" t="n">
-        <v>3.686129711202642</v>
+        <v>2.854887705085212</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>393.3921604325116</v>
+        <v>321.4858098391005</v>
       </c>
       <c r="I16" t="n">
-        <v>2442.459901415486</v>
+        <v>2483.576997494585</v>
       </c>
       <c r="J16" t="n">
-        <v>2.694478910772082</v>
+        <v>1.765988904426859</v>
       </c>
       <c r="K16" t="n">
-        <v>3.448263736336748</v>
+        <v>2.247127256655355</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1536412405893806</v>
+        <v>0.1265750137113751</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1121530661084678</v>
+        <v>0.08376006340310915</v>
       </c>
       <c r="F17" t="n">
-        <v>3.703253818990414</v>
+        <v>2.956327469728217</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>389.8468619509503</v>
+        <v>337.358064784251</v>
       </c>
       <c r="I17" t="n">
-        <v>2537.384236520515</v>
+        <v>2665.281676789051</v>
       </c>
       <c r="J17" t="n">
-        <v>2.497969399207014</v>
+        <v>1.703134166425535</v>
       </c>
       <c r="K17" t="n">
-        <v>3.075077501588781</v>
+        <v>2.257407765576341</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1354542565893837</v>
+        <v>0.1394826690910523</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09542899069074406</v>
+        <v>0.0996439037711937</v>
       </c>
       <c r="F18" t="n">
-        <v>3.384218781516888</v>
+        <v>3.501179516261852</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>390.2443870676665</v>
+        <v>393.4329286764859</v>
       </c>
       <c r="I18" t="n">
-        <v>2881.004974621463</v>
+        <v>2820.658159471113</v>
       </c>
       <c r="J18" t="n">
-        <v>2.380537621773903</v>
+        <v>1.773441938206338</v>
       </c>
       <c r="K18" t="n">
-        <v>2.991901472158265</v>
+        <v>2.376058570460994</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1363408333660704</v>
+        <v>0.1192291018087428</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09846104535581035</v>
+        <v>0.08059879925649471</v>
       </c>
       <c r="F19" t="n">
-        <v>3.599302966773239</v>
+        <v>3.086413875415122</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>419.7346581619117</v>
+        <v>369.1316638153421</v>
       </c>
       <c r="I19" t="n">
-        <v>3078.568964258409</v>
+        <v>3095.9862836799</v>
       </c>
       <c r="J19" t="n">
-        <v>2.270040433622865</v>
+        <v>1.503183985188219</v>
       </c>
       <c r="K19" t="n">
-        <v>2.866226220104054</v>
+        <v>2.221853669306116</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1324035295186386</v>
+        <v>0.1265928908337822</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0965524356970946</v>
+        <v>0.09050168797567393</v>
       </c>
       <c r="F20" t="n">
-        <v>3.693151739740612</v>
+        <v>3.507583034333314</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>430.7487666967266</v>
+        <v>418.2133158809168</v>
       </c>
       <c r="I20" t="n">
-        <v>3253.302750030464</v>
+        <v>3303.608228917335</v>
       </c>
       <c r="J20" t="n">
-        <v>2.191967796086555</v>
+        <v>1.788116061356879</v>
       </c>
       <c r="K20" t="n">
-        <v>2.648759281927748</v>
+        <v>2.145655032820109</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1290534761558634</v>
+        <v>0.1346690262651574</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09476424293365338</v>
+        <v>0.1006008776929196</v>
       </c>
       <c r="F21" t="n">
-        <v>3.763673434151682</v>
+        <v>3.952930579118675</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>446.6388169857011</v>
+        <v>471.0015041690706</v>
       </c>
       <c r="I21" t="n">
-        <v>3460.881723528905</v>
+        <v>3497.474640097934</v>
       </c>
       <c r="J21" t="n">
-        <v>2.136207383566929</v>
+        <v>1.942052565042098</v>
       </c>
       <c r="K21" t="n">
-        <v>2.691300192575502</v>
+        <v>2.206473662429797</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1255133369224385</v>
+        <v>0.1515834235265391</v>
       </c>
       <c r="E22" t="n">
-        <v>0.092637898460876</v>
+        <v>0.1196880635087397</v>
       </c>
       <c r="F22" t="n">
-        <v>3.817845260655218</v>
+        <v>4.752522731894157</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>452.873106472872</v>
+        <v>563.2719545006421</v>
       </c>
       <c r="I22" t="n">
-        <v>3608.167208180648</v>
+        <v>3715.920523473498</v>
       </c>
       <c r="J22" t="n">
-        <v>2.02918795095515</v>
+        <v>2.175099802968395</v>
       </c>
       <c r="K22" t="n">
-        <v>2.676320284562453</v>
+        <v>2.148787583222991</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1193646325841079</v>
+        <v>0.1488255151042939</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08768710138209734</v>
+        <v>0.1182077278778296</v>
       </c>
       <c r="F23" t="n">
-        <v>3.768116644662387</v>
+        <v>4.86075345692055</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>455.2628568104861</v>
+        <v>576.7866616628927</v>
       </c>
       <c r="I23" t="n">
-        <v>3814.051507172313</v>
+        <v>3875.589889668396</v>
       </c>
       <c r="J23" t="n">
-        <v>1.93276784838527</v>
+        <v>2.201252630244502</v>
       </c>
       <c r="K23" t="n">
-        <v>2.630663019490783</v>
+        <v>2.024698447482412</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1132105053409128</v>
+        <v>0.1431995609167998</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08263155724922011</v>
+        <v>0.1136547181897928</v>
       </c>
       <c r="F24" t="n">
-        <v>3.702236748021705</v>
+        <v>4.846854736711842</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>446.7653072212604</v>
+        <v>578.1776626457861</v>
       </c>
       <c r="I24" t="n">
-        <v>3946.323760996457</v>
+        <v>4037.565890175546</v>
       </c>
       <c r="J24" t="n">
-        <v>1.769994820502533</v>
+        <v>2.162988839474068</v>
       </c>
       <c r="K24" t="n">
-        <v>2.527794786391687</v>
+        <v>1.958072619018795</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1137619981471828</v>
+        <v>0.1345696857422607</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0846094322967611</v>
+        <v>0.1061015832995719</v>
       </c>
       <c r="F25" t="n">
-        <v>3.902297956580639</v>
+        <v>4.727033914999172</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>471.4898623310264</v>
+        <v>582.6727354714106</v>
       </c>
       <c r="I25" t="n">
-        <v>4144.528665196465</v>
+        <v>4329.895936499363</v>
       </c>
       <c r="J25" t="n">
-        <v>1.724641773577072</v>
+        <v>2.012297557616439</v>
       </c>
       <c r="K25" t="n">
-        <v>2.477689307763795</v>
+        <v>2.012332575045072</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1133561150106158</v>
+        <v>0.1268525001745644</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08529776421981261</v>
+        <v>0.09922125018008865</v>
       </c>
       <c r="F26" t="n">
-        <v>4.040013465359149</v>
+        <v>4.590907041843039</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>492.3676457357433</v>
+        <v>572.1933443684308</v>
       </c>
       <c r="I26" t="n">
-        <v>4343.547286263587</v>
+        <v>4510.698201304849</v>
       </c>
       <c r="J26" t="n">
-        <v>1.742372113925561</v>
+        <v>1.880631288098298</v>
       </c>
       <c r="K26" t="n">
-        <v>2.434162875981269</v>
+        <v>1.803995659180448</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1071268776304835</v>
+        <v>0.1202916238231049</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07990513609482741</v>
+        <v>0.09347124650063854</v>
       </c>
       <c r="F27" t="n">
-        <v>3.935342545595951</v>
+        <v>4.485083202850452</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>479.4593944067186</v>
+        <v>556.5839783987125</v>
       </c>
       <c r="I27" t="n">
-        <v>4475.621851507095</v>
+        <v>4626.955399797399</v>
       </c>
       <c r="J27" t="n">
-        <v>1.684404504554075</v>
+        <v>1.776960724069441</v>
       </c>
       <c r="K27" t="n">
-        <v>2.354635637465393</v>
+        <v>1.856083920513541</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1057154973688664</v>
+        <v>0.1229148959550506</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07941301199736261</v>
+        <v>0.09711827524784633</v>
       </c>
       <c r="F28" t="n">
-        <v>4.019220840757446</v>
+        <v>4.76476734492295</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>486.9198715499572</v>
+        <v>590.9270622726131</v>
       </c>
       <c r="I28" t="n">
-        <v>4605.945993433474</v>
+        <v>4807.611458978187</v>
       </c>
       <c r="J28" t="n">
-        <v>1.61835153631411</v>
+        <v>1.734416616034052</v>
       </c>
       <c r="K28" t="n">
-        <v>2.232141800456855</v>
+        <v>1.842483228199125</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1038606038689584</v>
+        <v>0.1220887034105516</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0784020982970538</v>
+        <v>0.09714804157562407</v>
       </c>
       <c r="F29" t="n">
-        <v>4.079603320611894</v>
+        <v>4.895166945392586</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>491.2493046432697</v>
+        <v>606.6296678816079</v>
       </c>
       <c r="I29" t="n">
-        <v>4729.890702956843</v>
+        <v>4968.761653907283</v>
       </c>
       <c r="J29" t="n">
-        <v>1.59091164153798</v>
+        <v>1.781483044916647</v>
       </c>
       <c r="K29" t="n">
-        <v>2.14811905187862</v>
+        <v>1.816446476856321</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.09846900095041315</v>
+        <v>0.1198302724095537</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07383700644086155</v>
+        <v>0.09578191919669998</v>
       </c>
       <c r="F30" t="n">
-        <v>3.997605671446127</v>
+        <v>4.982888905070847</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>484.5600901467915</v>
+        <v>619.5479412936713</v>
       </c>
       <c r="I30" t="n">
-        <v>4920.940453034609</v>
+        <v>5170.212241329067</v>
       </c>
       <c r="J30" t="n">
-        <v>1.48210142370289</v>
+        <v>1.850339883261562</v>
       </c>
       <c r="K30" t="n">
-        <v>2.045973748201694</v>
+        <v>1.941064144381521</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.09783094100908708</v>
+        <v>0.1176259889961043</v>
       </c>
       <c r="E31" t="n">
-        <v>0.07396403468657609</v>
+        <v>0.09428276119176837</v>
       </c>
       <c r="F31" t="n">
-        <v>4.099020614029659</v>
+        <v>5.038977042166208</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>506.2134613628309</v>
+        <v>619.3133756458557</v>
       </c>
       <c r="I31" t="n">
-        <v>5174.369745823165</v>
+        <v>5265.106639540067</v>
       </c>
       <c r="J31" t="n">
-        <v>1.433260408635041</v>
+        <v>1.80066839822411</v>
       </c>
       <c r="K31" t="n">
-        <v>1.92595060679974</v>
+        <v>1.867048845808558</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.09435206250613606</v>
+        <v>0.1205622231258689</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07113032051911394</v>
+        <v>0.09801253653935271</v>
       </c>
       <c r="F32" t="n">
-        <v>4.06309150101083</v>
+        <v>5.346514359004896</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>503.7762251150949</v>
+        <v>653.1778840577826</v>
       </c>
       <c r="I32" t="n">
-        <v>5339.3239292711</v>
+        <v>5417.765757154749</v>
       </c>
       <c r="J32" t="n">
-        <v>1.395231700390298</v>
+        <v>1.682295957579587</v>
       </c>
       <c r="K32" t="n">
-        <v>1.809089736002396</v>
+        <v>1.804927626947448</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.09356794357990479</v>
+        <v>0.119456158266358</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0710198824749273</v>
+        <v>0.09755208260134196</v>
       </c>
       <c r="F33" t="n">
-        <v>4.149711283124455</v>
+        <v>5.453604164504737</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>507.4294710666676</v>
+        <v>664.2713610290059</v>
       </c>
       <c r="I33" t="n">
-        <v>5423.112357207412</v>
+        <v>5560.79628433926</v>
       </c>
       <c r="J33" t="n">
-        <v>1.332255235244835</v>
+        <v>1.694654880126025</v>
       </c>
       <c r="K33" t="n">
-        <v>1.670549334079176</v>
+        <v>1.797462320081141</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.09728936868310104</v>
+        <v>0.1222283946163698</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07548476406191973</v>
+        <v>0.1010261819259438</v>
       </c>
       <c r="F34" t="n">
-        <v>4.461872635314538</v>
+        <v>5.764888618043331</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>551.1964034672167</v>
+        <v>699.3084641093221</v>
       </c>
       <c r="I34" t="n">
-        <v>5665.535822959435</v>
+        <v>5721.325771349572</v>
       </c>
       <c r="J34" t="n">
-        <v>1.361412122518245</v>
+        <v>1.744849739011568</v>
       </c>
       <c r="K34" t="n">
-        <v>1.578211940789238</v>
+        <v>1.828812591765107</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0988977614300664</v>
+        <v>0.1294514495952639</v>
       </c>
       <c r="E35" t="n">
-        <v>0.07784397080927341</v>
+        <v>0.109111530193284</v>
       </c>
       <c r="F35" t="n">
-        <v>4.697385055800565</v>
+        <v>6.364403272053455</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>582.4234953992807</v>
+        <v>771.4906474549005</v>
       </c>
       <c r="I35" t="n">
-        <v>5889.147408165856</v>
+        <v>5959.691064619228</v>
       </c>
       <c r="J35" t="n">
-        <v>1.344021149410771</v>
+        <v>1.751085097476655</v>
       </c>
       <c r="K35" t="n">
-        <v>1.516646728390403</v>
+        <v>1.822719503607904</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1023131228006478</v>
+        <v>0.1335090205367284</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08191114831884427</v>
+        <v>0.1138160437307449</v>
       </c>
       <c r="F36" t="n">
-        <v>5.01486377663598</v>
+        <v>6.779524591536787</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>625.7425036300251</v>
+        <v>819.7438527342938</v>
       </c>
       <c r="I36" t="n">
-        <v>6115.955475714043</v>
+        <v>6139.988514924218</v>
       </c>
       <c r="J36" t="n">
-        <v>1.380980349769698</v>
+        <v>1.752943381899874</v>
       </c>
       <c r="K36" t="n">
-        <v>1.472902712595847</v>
+        <v>1.730269819308834</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1086500417539542</v>
+        <v>0.1348259719741317</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08892990993435146</v>
+        <v>0.1156849536549753</v>
       </c>
       <c r="F37" t="n">
-        <v>5.509600176503423</v>
+        <v>7.043824405057776</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>685.9187549687533</v>
+        <v>843.6302967685807</v>
       </c>
       <c r="I37" t="n">
-        <v>6313.101623302319</v>
+        <v>6257.179417408121</v>
       </c>
       <c r="J37" t="n">
-        <v>1.36542377528292</v>
+        <v>1.833609420387906</v>
       </c>
       <c r="K37" t="n">
-        <v>1.388299971132925</v>
+        <v>1.773627892805363</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1119486744964674</v>
+        <v>0.1334840738768251</v>
       </c>
       <c r="E38" t="n">
-        <v>0.09280963730889125</v>
+        <v>0.1148091616758946</v>
       </c>
       <c r="F38" t="n">
-        <v>5.849232299372796</v>
+        <v>7.147775177768933</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>724.8582653675917</v>
+        <v>870.3362868618649</v>
       </c>
       <c r="I38" t="n">
-        <v>6474.916015110702</v>
+        <v>6520.150768435367</v>
       </c>
       <c r="J38" t="n">
-        <v>1.380151091840623</v>
+        <v>1.825344948246242</v>
       </c>
       <c r="K38" t="n">
-        <v>1.329951878481112</v>
+        <v>1.714624811930126</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1150218744362547</v>
+        <v>0.1335986490964878</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09642989700844495</v>
+        <v>0.115396940043893</v>
       </c>
       <c r="F39" t="n">
-        <v>6.186640172239324</v>
+        <v>7.339895869692648</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>765.4090319642503</v>
+        <v>890.5430794546455</v>
       </c>
       <c r="I39" t="n">
-        <v>6654.464950390295</v>
+        <v>6665.809014367174</v>
       </c>
       <c r="J39" t="n">
-        <v>1.413399556577735</v>
+        <v>1.789315765079764</v>
       </c>
       <c r="K39" t="n">
-        <v>1.295130211016425</v>
+        <v>1.690228515080693</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1189335366623673</v>
+        <v>0.1257547555564794</v>
       </c>
       <c r="E40" t="n">
-        <v>0.100952588430987</v>
+        <v>0.1079130158739585</v>
       </c>
       <c r="F40" t="n">
-        <v>6.614419614133871</v>
+        <v>7.048346057849878</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>815.9897496778354</v>
+        <v>866.8812287600517</v>
       </c>
       <c r="I40" t="n">
-        <v>6860.888632230754</v>
+        <v>6893.427011360338</v>
       </c>
       <c r="J40" t="n">
-        <v>1.409918721216019</v>
+        <v>1.728682386312754</v>
       </c>
       <c r="K40" t="n">
-        <v>1.215527685321818</v>
+        <v>1.644710455527791</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1219813121587861</v>
+        <v>0.1227218175675108</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1044909000503953</v>
+        <v>0.1052461565628795</v>
       </c>
       <c r="F41" t="n">
-        <v>6.974181706117017</v>
+        <v>7.022442100186542</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>864.3529171622284</v>
+        <v>866.6574495371267</v>
       </c>
       <c r="I41" t="n">
-        <v>7085.945394955902</v>
+        <v>7061.967193081765</v>
       </c>
       <c r="J41" t="n">
-        <v>1.444075554133148</v>
+        <v>1.760569874445786</v>
       </c>
       <c r="K41" t="n">
-        <v>1.177216619973364</v>
+        <v>1.650603569626342</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1177345381334197</v>
+        <v>0.1264908243526425</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1005698404317353</v>
+        <v>0.109496482413978</v>
       </c>
       <c r="F42" t="n">
-        <v>6.859109328902773</v>
+        <v>7.443113996950827</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>851.0754563107732</v>
+        <v>915.6514263084116</v>
       </c>
       <c r="I42" t="n">
-        <v>7228.76625503311</v>
+        <v>7238.876266279016</v>
       </c>
       <c r="J42" t="n">
-        <v>1.362269863154329</v>
+        <v>1.81658871180922</v>
       </c>
       <c r="K42" t="n">
-        <v>1.142697730068748</v>
+        <v>1.645806001656852</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1221396330711687</v>
+        <v>0.1261727619236615</v>
       </c>
       <c r="E43" t="n">
-        <v>0.105450272483168</v>
+        <v>0.1095600767891304</v>
       </c>
       <c r="F43" t="n">
-        <v>7.318412974969531</v>
+        <v>7.594964986207958</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>904.5968608548633</v>
+        <v>932.7911952816712</v>
       </c>
       <c r="I43" t="n">
-        <v>7406.251665483311</v>
+        <v>7392.968030976757</v>
       </c>
       <c r="J43" t="n">
-        <v>1.422612379956793</v>
+        <v>1.811283932181399</v>
       </c>
       <c r="K43" t="n">
-        <v>1.09925429260382</v>
+        <v>1.647674915793999</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1220609605161287</v>
+        <v>0.1290369765045594</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1057423910089936</v>
+        <v>0.1128480727221163</v>
       </c>
       <c r="F44" t="n">
-        <v>7.479881153967487</v>
+        <v>7.970705011200325</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>918.7292621490581</v>
+        <v>978.9287468138829</v>
       </c>
       <c r="I44" t="n">
-        <v>7526.806755118563</v>
+        <v>7586.4203682678</v>
       </c>
       <c r="J44" t="n">
-        <v>1.452589736761587</v>
+        <v>1.82822368288149</v>
       </c>
       <c r="K44" t="n">
-        <v>1.08294003160162</v>
+        <v>1.65831453647056</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1224822807889025</v>
+        <v>0.1272599467676901</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1065852206582666</v>
+        <v>0.1114494385569599</v>
       </c>
       <c r="F45" t="n">
-        <v>7.704712681614773</v>
+        <v>8.049073759774625</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>945.9318763873773</v>
+        <v>991.7280504577794</v>
       </c>
       <c r="I45" t="n">
-        <v>7723.009975766909</v>
+        <v>7792.931520458314</v>
       </c>
       <c r="J45" t="n">
-        <v>1.48193769526809</v>
+        <v>1.800662536317504</v>
       </c>
       <c r="K45" t="n">
-        <v>1.057437176339367</v>
+        <v>1.657229075286269</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1206446608299852</v>
+        <v>0.1289775804573678</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1050532541071126</v>
+        <v>0.1135339205363991</v>
       </c>
       <c r="F46" t="n">
-        <v>7.737894532184799</v>
+        <v>8.351490586907332</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>944.9599637287699</v>
+        <v>1019.795978682015</v>
       </c>
       <c r="I46" t="n">
-        <v>7832.588340236835</v>
+        <v>7906.76933980087</v>
       </c>
       <c r="J46" t="n">
-        <v>1.554015781451876</v>
+        <v>1.877513925826625</v>
       </c>
       <c r="K46" t="n">
-        <v>1.040965842293198</v>
+        <v>1.718144492644945</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1195707540536134</v>
+        <v>0.1280102816955088</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1042855240892665</v>
+        <v>0.1128715713082781</v>
       </c>
       <c r="F47" t="n">
-        <v>7.822633636033864</v>
+        <v>8.455824731509718</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>955.2299584915445</v>
+        <v>1032.198214137021</v>
       </c>
       <c r="I47" t="n">
-        <v>7988.826080859505</v>
+        <v>8063.40084925565</v>
       </c>
       <c r="J47" t="n">
-        <v>1.61212674302741</v>
+        <v>1.920547467088479</v>
       </c>
       <c r="K47" t="n">
-        <v>1.031291035513255</v>
+        <v>1.751287524883302</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1239856131712584</v>
+        <v>0.1316975343847367</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1090874093136268</v>
+        <v>0.1169304856497834</v>
       </c>
       <c r="F48" t="n">
-        <v>8.32218530207226</v>
+        <v>8.918338169563292</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1010.664088048337</v>
+        <v>1076.997671953299</v>
       </c>
       <c r="I48" t="n">
-        <v>8151.462594715167</v>
+        <v>8177.8119612095</v>
       </c>
       <c r="J48" t="n">
-        <v>1.738570708180128</v>
+        <v>2.016712525405009</v>
       </c>
       <c r="K48" t="n">
-        <v>1.019519235432884</v>
+        <v>1.78459501168529</v>
       </c>
     </row>
     <row r="49">
@@ -2136,28 +2136,28 @@
         <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1291762543223363</v>
+        <v>0.1309837896840974</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1146625252277086</v>
+        <v>0.1165001861788323</v>
       </c>
       <c r="F49" t="n">
-        <v>8.900280105831035</v>
+        <v>9.043591233112839</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1070.792026399236</v>
+        <v>1092.407163953366</v>
       </c>
       <c r="I49" t="n">
-        <v>8289.387488564778</v>
+        <v>8340.018002135988</v>
       </c>
       <c r="J49" t="n">
-        <v>1.905197556405317</v>
+        <v>2.008008885346374</v>
       </c>
       <c r="K49" t="n">
-        <v>1.004144664826493</v>
+        <v>1.756283950885846</v>
       </c>
     </row>
   </sheetData>
